--- a/_build/utils/dm-dependencies/resources/attribution_source.xlsx
+++ b/_build/utils/dm-dependencies/resources/attribution_source.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55363070-C634-4D71-B99A-0D8D67231EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3B9E46C-0938-4237-9D8F-F11E9D138832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14,6 +14,9 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -73,12 +76,36 @@
         </r>
       </text>
     </comment>
+    <comment ref="A337" authorId="0" shapeId="0" xr:uid="{F29F88B6-0DCB-4668-AB16-B64585FC3D2F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+GUM12</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3041" uniqueCount="1816">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3348" uniqueCount="1999">
   <si>
     <t>ID</t>
   </si>
@@ -9914,9 +9941,6 @@
     </r>
   </si>
   <si>
-    <t>GUM_speech_school</t>
-  </si>
-  <si>
     <t>(1168, 1178)</t>
   </si>
   <si>
@@ -12916,6 +12940,1306 @@
   </si>
   <si>
     <t>many , many other case law citations</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">So that we will have an adequate factual base, I am requesting </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> that the Tariff Commission make a broad survey of the competitiveness of particular industries. [..]</t>
+    </r>
+  </si>
+  <si>
+    <t>GUM_letter_trade</t>
+  </si>
+  <si>
+    <t>(590, 592)</t>
+  </si>
+  <si>
+    <t>(593, 607)</t>
+  </si>
+  <si>
+    <t>I am requesting</t>
+  </si>
+  <si>
+    <t>(580, 592)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I didn`t see anything to suggest </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> this was a county way. [..]</t>
+    </r>
+  </si>
+  <si>
+    <t>GUM_court_way</t>
+  </si>
+  <si>
+    <t>(982, 983)</t>
+  </si>
+  <si>
+    <t>(984, 989)</t>
+  </si>
+  <si>
+    <t>to suggest</t>
+  </si>
+  <si>
+    <t>(977, 983)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">We have disputed the-- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> whether that was effective [..]</t>
+    </r>
+  </si>
+  <si>
+    <t>(1018, 1022)</t>
+  </si>
+  <si>
+    <t>(1023, 1026)</t>
+  </si>
+  <si>
+    <t>We have disputed the --</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The rise in walking for recreation, transportation and exercise is also being fueled by new research showing </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> it ’s good for us in many ways besides better health: [..]</t>
+    </r>
+  </si>
+  <si>
+    <t>GUM_essay_walking</t>
+  </si>
+  <si>
+    <t>(883, 883)</t>
+  </si>
+  <si>
+    <t>(884, 895)</t>
+  </si>
+  <si>
+    <t>showing</t>
+  </si>
+  <si>
+    <t>(866, 883)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">walking and public transit </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (which involves a walk) represent important pathways to opportunity. [..]</t>
+    </r>
+  </si>
+  <si>
+    <t>(1342, 1347)</t>
+  </si>
+  <si>
+    <t>(1338, 1341)</t>
+  </si>
+  <si>
+    <t>( which involves a walk )</t>
+  </si>
+  <si>
+    <t>(1342, 1353)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">To convince parliamentarians </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> that the party through which they were elected is a disaster, [..]</t>
+    </r>
+  </si>
+  <si>
+    <t>GUM_letter_srilanka</t>
+  </si>
+  <si>
+    <t>(568, 570)</t>
+  </si>
+  <si>
+    <t>(571, 582)</t>
+  </si>
+  <si>
+    <t>To convince parliamentarians</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dear Sir, The IHT.com article by Charu Hogg regarding the Human Rights situation in Sri Lanka makes interesting reading, though the mixture of fact and fiction perhaps justifies Ms Hogg ’s arriving here on a tourist visa to complete her research in this field . Though datelined August 15th, the article does not take into account the refutations of salient points in her report which I sent to Brad Adams, the Director of the institute for which she works . I had for instance challenged the assertions of the sensationalistic press release that accompanied the release of the report, which alleged indiscriminate attacks which led to displacement, after which ‘ Government authorities have forced some to return to areas that remain insecure ’ . As I noted then, the release ignored the substance of the report which relates the current situation according to the UNHCR spokesperson who said that ‘ Our staff monitoring the situation on the ground say the majority of people are eager to return home, the returns are voluntary and in line with international protection standards.... UNHCR will continue to monitor the returns and report directly to the government on any problems regarding the voluntariness and any deviation from the civilian characteristics of the move ’ . (p 32) Again, the claim of indiscriminate attacks is strange given that the report only records one, as to which the government had explained at the time that its radar showed that mortars had been launched from a refugee camp, ie it was not indiscriminate at all . Of course I cannot claim for certain that the government was correct, but one such incident in a campaign in which very few civilian lives were lost does not justify Ms Hogg ’s extravagant claims, and suggests a greater care about civilians than is common in countries to which Ms Hogg owes allegiance . I would have more respect for her if similar language were used about much greater assaults on individual lives and liberties by other countries engaged in wars against terrorism . But the excesses of her account are not my point here . Even Human Rights researchers have to live, and without exaggerations they may not be taken seriously in an increasingly dangerous world . Much more serious is the congruence of her recommendations with those of the LTTE and also the main opposition party, both of which dream of getting rid of the duly elected government – elected not only at the Presidential election of 2005 but also at the Parliamentary election of 2004 . How does one get rid of an elected government? One is by winning over members of Parliament . The opposition UNP has done this twice before so far, once in 1964 when the current leader ’s father presided over a massive bribery operation, and again in 2001 when once again there were allegations of bribery . But in both cases there were members of Parliament who felt genuinely that the government was failing, and therefore they crossed over to the opposition . This precipitated an election which the opposition won, though in both instances not especially convincingly, and in both cases only to be trounced at the next election . To convince parliamentarians that the party through which they were elected is a disaster, you have to work extra hard . In 1964 there were allegations that communists were taking over the government, in 2001 the task was simpler since a terrorist assault on the airport reduced confidence considerably and contributed to negative growth of the economy . Hence the terrorism that the LTTE has threatened, in making clear its intention of attacking not only military but also economic targets . Of a piece with this is the opposition UNP ’s attempt to prevent the government raising bonds by threatening not to repay them if it returns to power . It assumes this will happen soon because, according to sympathetic media, Saturn has moved . Saturn ’s movements may be as good a way of predicting events as any other, but what is sad is to see some members of the international community also falling in with the plans of a terrorist organization and an opposition leadership that has been convincingly trounced in elections twice in the recent past . Now, sadly, both feel that, by presenting Sri Lanka as a failed state, and requiring that it be nannied by others, they will once more be able to topple an elected government . Whilst we are grateful to those who draw attention to particular violations of human rights, and believe the government has an obligation to take action to deal with perpetrators and prevent repetition, the relentless generalizations culminating in calls for a particular agenda will only promote the cause of undemocratic terrorism at this juncture . It is easy for Ms Hogg, in her London retreat, to pontificate, but could she live amongst our Tamil fellow citizens who have now got to offer one member of each family to the relentless LTTE war machine, if she had been present when Tamil groups not associated with the LTTE were decimated on the last occasion the LTTE and the UNP worked together, she would think twice about what she is trying to achieve . </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Yours sincerely, Rajiva Wijesinha . Secretary General Secretariat for Coordinating the Peace Process [..]</t>
+    </r>
+  </si>
+  <si>
+    <t>(929, 942)</t>
+  </si>
+  <si>
+    <t>(5, 928)</t>
+  </si>
+  <si>
+    <t>Rajiva Wijesinha .</t>
+  </si>
+  <si>
+    <t>(929, 934)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">She speaks from long experience of University life, and I fancy </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> her opinion would be confirmed by anyone else of like affiliations. [..]</t>
+    </r>
+  </si>
+  <si>
+    <t>GUM_letter_travel</t>
+  </si>
+  <si>
+    <t>(232, 234)</t>
+  </si>
+  <si>
+    <t>(235, 246)</t>
+  </si>
+  <si>
+    <t>and I fancy</t>
+  </si>
+  <si>
+    <t>(223, 234)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">My great regret in leaving Florence was that I had seen so little of you . I wanted so much to have at least one more talk with you . Next year I hope I may come back with more leisure, and perhaps before that you may come to America . You say that you have given up the idea for the present; but in the hope that you may turn to it again later, I will tell you what I learned from my friend, Professor Norton`s daughter . She writes me that it is customary for the Faculties of the various colleges to invite people to give lectures, and she thought that you might be probably be invited by Radcliffe or Barnard, if they knew of your visit . She says, however, that in giving a lecture or course of lectures before one of our girls` colleges, or one of the Universities, you would probably be asked to deal with a more concrete subject than, say, Life and Art . In other words, a lecture or lectures on a special period of Italian history or art would be more desirable than a discussion of aesthetics . She speaks from long experience of University life, and I fancy her opinion would be confirmed by anyone else of like affiliations . She adds that, from the financial standpoint, the lecture to a general audience, which you dislike, would of course be more successful . Such lectures, I am sure, could be arranged for and carried out successfully in New York and Boston, and perhaps Washington; but your books on Italian art and life are so much appreciated in America that if you dealt with that subject there w[oul]d be far more certainty of popularity . Whenever you feel disposed to take up the matter again, write me and I will do all I can to make satisfactory arrangements for you, in one line or the other, or in both; and if you should come to America this summer or autumn, I need not say how much we should enjoy a visit from you . We could show you some corners of old New England, and some of the most charming woodland scenery I know of anywhere; and the pleasure of welcoming you would be great . If you are not weary of this long letter I should like to go on to talk about your play; but you can let my remarks wait till you have an unemployed hour . You said you wished my impression of it — but was it from the standpoint of the stage or of the “ closet ”? On the former I should hardly be an authority; so I prefer to write of the play as a reader, rather than as a spectator . — It is exquisite, and so completely the kind of fanciful poetical thing that I long to see done, that I have only one objection to make to it: namely, its greater fitness for narrative than for dramatic treatment . Certainly the idea is dramatic; but even for a play read in the closet it seems to me to lack movement and clash of emotions . In short, whatever is faulty in it seems to me faulty only from the dramatic point - of - view; whatever is most exquisite, would increase in value were the form narrative . I have always thought, for instance, that no one has your gift of suggesting in a few touches an Italian landscape or picture; and the little stage directions at the head of each act are so beautiful that one feels they ought to be, not the mere illuminated border of the page, but its central subject . All your little touches of description, of characterization, of local colour in the good sense, would gain immensely, would find their true place, in a story, whereas they are effaced, in the play, by the need of stage - fare - shortening, and compression, and by the fact that the reader, inevitably, from force of association, is on the alert for effects of another sort . — I feel a kind of shyness in saying this, because I have done so little to prove my fitness to express an opinion on your work, and because my very great and increasing admiration for what you have done makes any kind of criticism, even of this one little thing, seem like an impertinence . But you asked me to tell you, and I was too sincerely interested to give a superficial answer . The whole little romance lives in my memory like a more delicate, a paler, Pinturricchio; and I should be sorry indeed not to see more use made of Hyppolita, who seems to me a most original creation . I wish you would put it all into a story — a long short story, full of such curious colour and detail as you alone could give, and give one of our magazines a chance to publish it . I have no space left to tell you of the Brenta, which I saw and photographed, in its whole length, nor of Countess Papafava`s kindness and good advice about villas . Here Donna Giulia Bassi is arranging “ combinazioni ” with infinite amiability, and all this, too, I owe indirectly to you . Don`t think of answering this, but remember that when I can be of use to you, a line to THE MOUNT, LENOX, MASSACHUSETTS will always find me . </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Gratefully yours E. WHARTON [..]</t>
+    </r>
+  </si>
+  <si>
+    <t>(1019, 1022)</t>
+  </si>
+  <si>
+    <t>(11, 1018)</t>
+  </si>
+  <si>
+    <t>E. WHARTON</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Elite private universities have made clear time and again </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> that their admissions decisions are made through a holistic decisionmaking process that involves a series of discussions among the admissions team. [..]</t>
+    </r>
+  </si>
+  <si>
+    <t>GUM_essay_merit</t>
+  </si>
+  <si>
+    <t>(275, 283)</t>
+  </si>
+  <si>
+    <t>(284, 305)</t>
+  </si>
+  <si>
+    <t>Elite private universities have made clear time and again</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sirs: I was astounded to read the statement by Francis Russell in your correspondence column of March 23 that “ James Cannon who organized the International Labor Defense to aid Sacco and Vanzetti admitted privately that he thought Sacco was guilty . ” (Emphasis added .) After reading this revelation of my private thoughts about a case that began 43 years ago, I managed to get a copy of Mr. Russell ’s book Tragedy in Dedham which I had previously missed . There I found on page 332 that Mr. Russell had explained my attitude somewhat differently, as follows: “ After his expulsion from the party, James Cannon, the International Labor Defense ’s executive secretary, was to admit privately — much as Moore did — that he felt Sacco was guilty . ” (Emphasis added .) The truth is that I have never felt or thought that Sacco was guilty . I have always thought they were innocent, and have never expressed a different thought or feeling, privately or publicly, anywhere at any time . I would like to add a word in defense of the memory of Carlo Tresca which has been besmirched by Mr. Russell ’s statement that Tresca privately told Max Eastman “ that Sacco was guilty . ” I knew Carlo Tresca very well and was closely associated with him in the campaign for Sacco and Vanzetti, and for 25 years after that . We collaborated over the years in many activities of common interest during which we had occasion to visit each other ’s offices, to drink wine together at Italian restaurants, and to talk of many things in friendly, casual conversation . It would not be too much to say that we were friends . Never, at any time, did I ever hear him express or even intimate any doubt about the innocence of Sacco and Vanzetti . And I never heard any report, or rumor, or gossip, from anyone else who ever heard such a thing about Tresca until Mr. Russell ’s statement hit me in the eye . </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> James P. Cannon Los Angeles, Calif. [..]</t>
+    </r>
+  </si>
+  <si>
+    <t>GUM_letter_sacco</t>
+  </si>
+  <si>
+    <t>(381, 387)</t>
+  </si>
+  <si>
+    <t>(12, 380)</t>
+  </si>
+  <si>
+    <t>James P. Cannon</t>
+  </si>
+  <si>
+    <t>(381, 383)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mr. James P. Cannon 1902 Hyperion Ave. Los Angeles 27, California Dear Mr. Cannon: I congratulate you on that wonderful letter you wrote to the New Republic, repudiating Francis Russell ’s statement about you in connection with the Sacco - Vanzetti case . You undoubtedly know I wrote a review of Russell ’s book, in which I uncovered other misstatements of his . I enclose a copy of it herewith just in case you did not see it . I would be grateful if you would write me telling just how Russell got around to misquoting and misrepresenting you . </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> In appreciation of your reply, I am, Sincerely yours, (signed M. A. Musmanno) [..]</t>
+    </r>
+  </si>
+  <si>
+    <t>(409, 512)</t>
+  </si>
+  <si>
+    <t>( signed M. A. Musmanno )</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">SUPREME COURT OF PENNSYLVANIA Justice Michael A. Musmanno 811 City - County Building Pittsburgh 19, Pennsylvania </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> May 13, 1963 Mr. James P. Cannon 1902 Hyperion Ave. Los Angeles 27, California Dear Mr. Cannon: I congratulate you on that wonderful letter you wrote to the New Republic, repudiating Francis Russell ’s statement about you in connection with the Sacco - Vanzetti case . You undoubtedly know I wrote a review of Russell ’s book, in which I uncovered other misstatements of his . I enclose a copy of it herewith just in case you did not see it . I would be grateful if you would write me telling just how Russell got around to misquoting and misrepresenting you . In appreciation of your reply, I am, Sincerely yours, (signed M. A. Musmanno) P.S. I enclose herewith also copy of the speech I made in Massachusetts when I was supporting the bill for a posthumous pardon for the two cruelly executed innocent men. [..]</t>
+    </r>
+  </si>
+  <si>
+    <t>(388, 404)</t>
+  </si>
+  <si>
+    <t>(405, 561)</t>
+  </si>
+  <si>
+    <t>SUPREME COURT OF PENNSYLVANIA</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">James P. Cannon 1902 Hyperion Ave. Los Angeles 27, Calif. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> May 23, 1963 Justice Michael A. Musmanno 811 City - County Building Pittsburgh 19, Pennsylvania Dear Justice Musmanno: I received your letter of May 13th with the two enclosures . I especially appreciated receiving a copy of your speech before the Massachusetts Legislature, as reprinted in the Congressional Record . I had read your review of Francis Russell ’s book at the time it appeared in the New Republic and referred to it in a paragraph of my letter to the editor, but this paragraph was eliminated in the editing . (A carbon copy of my original letter is enclosed .) I salute your speech and review as mighty contributions to the counter-offensive against the defamers of Sacco ’s memory . Mr. Russell is obviously a very careless historian: he did not bother to check with me before rushing into print with a completely false statement, attributing to me an opinion about Sacco ’s guilt, which I never held and never expressed anywhere . The case is made all the worse for Mr. Russell by the fact that he had written me under date of Oct. 7, 1960 . This letter (reproduced from New York) dealt with a wild rumor he had heard somewhere or other about a matter of which I had no knowledge and did not bother to deny . There was no inquiry as to my opinion about Sacco ’s guilt or innocence . (For your information I enclose the original of Mr. Russell ’s Oct. 7, 1960 letter . This is the only communication I received from him .) Sincerely yours, James P. Cannon JPC: dn encl. (2) [..]</t>
+    </r>
+  </si>
+  <si>
+    <t>(562, 572)</t>
+  </si>
+  <si>
+    <t>(573, 864)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Justice Michael A. Musmanno 811 City - County Building Pittsburgh 19, Pennsylvania Dear Justice Musmanno: I received your letter of May 13th with the two enclosures . I especially appreciated receiving a copy of your speech before the Massachusetts Legislature, as reprinted in the Congressional Record . I had read your review of Francis Russell ’s book at the time it appeared in the New Republic and referred to it in a paragraph of my letter to the editor, but this paragraph was eliminated in the editing . (A carbon copy of my original letter is enclosed .) I salute your speech and review as mighty contributions to the counter-offensive against the defamers of Sacco ’s memory . Mr. Russell is obviously a very careless historian: he did not bother to check with me before rushing into print with a completely false statement, attributing to me an opinion about Sacco ’s guilt, which I never held and never expressed anywhere . The case is made all the worse for Mr. Russell by the fact that he had written me under date of Oct. 7, 1960 . This letter (reproduced from New York) dealt with a wild rumor he had heard somewhere or other about a matter of which I had no knowledge and did not bother to deny . There was no inquiry as to my opinion about Sacco ’s guilt or innocence . (For your information I enclose the original of Mr. Russell ’s Oct. 7, 1960 letter . This is the only communication I received from him .) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Sincerely yours, James P. Cannon JPC: dn [..]</t>
+    </r>
+  </si>
+  <si>
+    <t>(852, 860)</t>
+  </si>
+  <si>
+    <t>(577, 851)</t>
+  </si>
+  <si>
+    <t>(852, 857)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Supreme Court of Pennsylvania Justice Michael A. Musmanno 811 City - County Building Pittsburgh 19, Pennsylvania </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> May 27, 1963 Mr. James P. Cannon 1902 Hyperion Avenue Los Angeles 27, California Dear Mr. Cannon: I was delighted to receive your letter and appreciate your submitting further proof of Francis Russell ’s deceptions, trickery and general unreliability . Please let me know if I may quote you in connection with your repudiation of Russell ’s statements concerning you . I am sending you with this letter my full - length review of Russell ’s book, printed in the current issue of the Kansas Law Review . I am sure you will find it interesting . I am sorry I did not know, as I was writing the review, of the manner in which Russell treated you . I certainly would have given him a blast on it . With renewed expression of gratitude for your letter and cooperation in the cause of truth, I am, with best wishes, Sincerely yours, Signed — Michael Musmanno [..]</t>
+    </r>
+  </si>
+  <si>
+    <t>(865, 881)</t>
+  </si>
+  <si>
+    <t>(882, 1048)</t>
+  </si>
+  <si>
+    <t>Supreme Court of Pennsylvania</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mr. James P. Cannon 1902 Hyperion Avenue Los Angeles 27, California Dear Mr. Cannon: I was delighted to receive your letter and appreciate your submitting further proof of Francis Russell ’s deceptions, trickery and general unreliability . Please let me know if I may quote you in connection with your repudiation of Russell ’s statements concerning you . I am sending you with this letter my full - length review of Russell ’s book, printed in the current issue of the Kansas Law Review . I am sure you will find it interesting . I am sorry I did not know, as I was writing the review, of the manner in which Russell treated you . I certainly would have given him a blast on it . </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> With renewed expression of gratitude for your letter and cooperation in the cause of truth, I am, with best wishes, Sincerely yours, Signed — Michael Musmanno [..]</t>
+    </r>
+  </si>
+  <si>
+    <t>(1019, 1048)</t>
+  </si>
+  <si>
+    <t>(886, 1018)</t>
+  </si>
+  <si>
+    <t>Michael Musmanno</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">It would not be too much to say </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> that we were friends. [..]</t>
+    </r>
+  </si>
+  <si>
+    <t>40-41</t>
+  </si>
+  <si>
+    <t>(308, 315)</t>
+  </si>
+  <si>
+    <t>(316, 320)</t>
+  </si>
+  <si>
+    <t>It would not be too much to say</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I considered him on trial a good and trustworthy umpire, and arranged with the MCC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> that he should accompany us to NSW. [..]</t>
+    </r>
+  </si>
+  <si>
+    <t>GUM_letter_cricket</t>
+  </si>
+  <si>
+    <t>(390, 394)</t>
+  </si>
+  <si>
+    <t>(395, 402)</t>
+  </si>
+  <si>
+    <t>and arranged with the MCC</t>
+  </si>
+  <si>
+    <t>(379, 394)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I implored Gregory, as a friend, and for the sake of the NSW Cricket Association, which I warned him </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> would be the sufferer by it, [..]</t>
+    </r>
+  </si>
+  <si>
+    <t>(544, 546)</t>
+  </si>
+  <si>
+    <t>(547, 553)</t>
+  </si>
+  <si>
+    <t>I warned him</t>
+  </si>
+  <si>
+    <t>(525, 546)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I don`t suppose that they would have done so, but I determined to obey the laws of cricket, and may add </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> that for one hour and a half I never left the ground, surrounded the whole time, with two short intervals, by some hundreds of people. [..]</t>
+    </r>
+  </si>
+  <si>
+    <t>(748, 750)</t>
+  </si>
+  <si>
+    <t>(751, 779)</t>
+  </si>
+  <si>
+    <t>and may add</t>
+  </si>
+  <si>
+    <t>(727, 750)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">His answer was, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ` I shall give it you in two minutes` time if the batsmen do not return`. [..]</t>
+    </r>
+  </si>
+  <si>
+    <t>(888, 891)</t>
+  </si>
+  <si>
+    <t>(892, 910)</t>
+  </si>
+  <si>
+    <t>His answer was ,</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Beyond slyly kicking me once or twice the mob behaved very well, their one cry being, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ` Change your umpire`. [..]</t>
+    </r>
+  </si>
+  <si>
+    <t>(1080, 1084)</t>
+  </si>
+  <si>
+    <t>(1085, 1090)</t>
+  </si>
+  <si>
+    <t>their one cry being ,</t>
+  </si>
+  <si>
+    <t>(1067, 1084)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Second, the district court incorrectly ruled that claim or issue preclusion categorically had no impact on either A., the state`s ability to proceed on its second successive petition, or B., do so by use of the same exact evidence presented at the previous jury trial that had ended with dismissal on the merits, on that jury`s finding </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> that T. W. did not require commitment. [..]</t>
+    </r>
+  </si>
+  <si>
+    <t>GUM_court_mental</t>
+  </si>
+  <si>
+    <t>(398, 411)</t>
+  </si>
+  <si>
+    <t>(412, 419)</t>
+  </si>
+  <si>
+    <t>that had ended with dismissal on the merits , on that jury &amp;apos;s finding</t>
+  </si>
+  <si>
+    <t>(348, 411)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">5321 119 expressly provides </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> a capable respondent may waive their right to be present and participate, [..]</t>
+    </r>
+  </si>
+  <si>
+    <t>(771, 774)</t>
+  </si>
+  <si>
+    <t>(775, 787)</t>
+  </si>
+  <si>
+    <t>5321 119 expressly provides</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">5321 140 piggybacks 119 on a person`s presence by Zoom, making it subject to the waiver provisions of 119 and providing in subsection five, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> the respondent can choose not to appear by Zoom at all. [..]</t>
+    </r>
+  </si>
+  <si>
+    <t>(835, 840)</t>
+  </si>
+  <si>
+    <t>(841, 852)</t>
+  </si>
+  <si>
+    <t>and providing in subsection five ,</t>
+  </si>
+  <si>
+    <t>(814, 840)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">This court has consistently interpreted it in such a way that, um, that the court`s only discretion is to ensure that the waiver is knowing and voluntary and relevant to this in this regard is this court`s decision in in re PAC, a 2013 decision, in which case the respondent`s attorney represented </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> that the respondent didn`t wish to be present, [..]</t>
+    </r>
+  </si>
+  <si>
+    <t>(961, 968)</t>
+  </si>
+  <si>
+    <t>(969, 978)</t>
+  </si>
+  <si>
+    <t>in which case the respondent &amp;apos;s attorney represented</t>
+  </si>
+  <si>
+    <t>(910, 968)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">And then I have a note here </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> that you want to split your time, uh, saving 15 minutes for rebuttal. [..]</t>
+    </r>
+  </si>
+  <si>
+    <t>GUM_court_mountain</t>
+  </si>
+  <si>
+    <t>(84, 90)</t>
+  </si>
+  <si>
+    <t>(91, 106)</t>
+  </si>
+  <si>
+    <t>And then I have a note here</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The appellants don`t disagree </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> that the commercial use prohibition is somewhat broad, [..]</t>
+    </r>
+  </si>
+  <si>
+    <t>(1065, 1069)</t>
+  </si>
+  <si>
+    <t>(1070, 1078)</t>
+  </si>
+  <si>
+    <t>The appellants do n&amp;apos;t disagree</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">This extreme clampdown on free expression spurred culture - jammers, such as the self - styled Barbie Liberation Organization, which substituted voice boxes of GI Joe with those in Barbie, so that GI Joe would say, “ Let ’s plan our dream wedding, ” and Barbie would yell, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> “ Vengeance is mine! ” [..]</t>
+    </r>
+  </si>
+  <si>
+    <t>GUM_essay_privatization</t>
+  </si>
+  <si>
+    <t>(743, 747)</t>
+  </si>
+  <si>
+    <t>(748, 753)</t>
+  </si>
+  <si>
+    <t>and Barbie would yell ,</t>
+  </si>
+  <si>
+    <t>(694, 747)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">No matter; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Mattel wanted to send a message that you ca n’t mess with Barbie. [..]</t>
+    </r>
+  </si>
+  <si>
+    <t>(840, 842)</t>
+  </si>
+  <si>
+    <t>(843, 856)</t>
+  </si>
+  <si>
+    <t>No matter ;</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A Citigroup economist exulted, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> `` Water as an asset class will, in my view, become eventually the single most important physical - commodity based asset class, dwarfing oil, copper, agricultural commodities and precious metals . `` [..]</t>
+    </r>
+  </si>
+  <si>
+    <t>GUM_essay_public</t>
+  </si>
+  <si>
+    <t>(589, 593)</t>
+  </si>
+  <si>
+    <t>(594, 630)</t>
+  </si>
+  <si>
+    <t>A Citigroup economist exulted ,</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">So it`s not always just a .08, that`s the legal limit and we consider </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> if you`re over a .08, regardless of how you feel, you`re legally intoxicated. [..]</t>
+    </r>
+  </si>
+  <si>
+    <t>GUM_court_crash</t>
+  </si>
+  <si>
+    <t>(1229, 1231)</t>
+  </si>
+  <si>
+    <t>(1232, 1249)</t>
+  </si>
+  <si>
+    <t>and we consider</t>
+  </si>
+  <si>
+    <t>(1215, 1231)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">So you want us to defer to the judge`s findings, the first finding, and then ignore the judge`s finding later on and say </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> there`s an abuse of discretion? [..]</t>
+    </r>
+  </si>
+  <si>
+    <t>GUM_court_nullification</t>
+  </si>
+  <si>
+    <t>(796, 797)</t>
+  </si>
+  <si>
+    <t>(798, 804)</t>
+  </si>
+  <si>
+    <t>and say</t>
+  </si>
+  <si>
+    <t>(771, 797)</t>
+  </si>
+  <si>
+    <t>anything</t>
+  </si>
+  <si>
+    <t>new research</t>
+  </si>
+  <si>
+    <t>a report by the Leadership Conference Education Fund</t>
+  </si>
+  <si>
+    <t>Rajiva Wijesinha</t>
+  </si>
+  <si>
+    <t>Barbie</t>
+  </si>
+  <si>
+    <t>Elite private universities</t>
+  </si>
+  <si>
+    <t>M. A. Musmanno</t>
+  </si>
+  <si>
+    <t>Justice Michael A. Musmanno</t>
+  </si>
+  <si>
+    <t>His</t>
+  </si>
+  <si>
+    <t>that jury 's</t>
+  </si>
+  <si>
+    <t>5321 119</t>
+  </si>
+  <si>
+    <t>5321 140</t>
+  </si>
+  <si>
+    <t>the respondent 's attorney</t>
+  </si>
+  <si>
+    <t>a note</t>
+  </si>
+  <si>
+    <t>The appellants</t>
+  </si>
+  <si>
+    <t>Mattel</t>
+  </si>
+  <si>
+    <t>A Citigroup economist</t>
+  </si>
+  <si>
+    <t>GUM_speech_open</t>
   </si>
 </sst>
 </file>
@@ -13043,7 +14367,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -13107,6 +14431,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -13394,7 +14721,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P336"/>
+  <dimension ref="A1:P370"/>
   <sheetFormatPr defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="25.26953125" customWidth="1"/>
@@ -14465,7 +15792,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>136</v>
@@ -14705,7 +16032,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>165</v>
@@ -15425,7 +16752,7 @@
         <v>44</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="C43" s="9" t="s">
         <v>245</v>
@@ -16673,7 +18000,7 @@
         <v>70</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="C69" s="9" t="s">
         <v>393</v>
@@ -17969,7 +19296,7 @@
         <v>97</v>
       </c>
       <c r="B96" s="17" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="C96" s="9" t="s">
         <v>543</v>
@@ -18449,7 +19776,7 @@
         <v>107</v>
       </c>
       <c r="B106" s="18" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="C106" s="9" t="s">
         <v>597</v>
@@ -21425,7 +22752,7 @@
         <v>169</v>
       </c>
       <c r="B168" s="8" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="C168" s="9" t="s">
         <v>931</v>
@@ -22145,7 +23472,7 @@
         <v>184</v>
       </c>
       <c r="B183" s="19" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="C183" s="9" t="s">
         <v>1009</v>
@@ -22241,7 +23568,7 @@
         <v>186</v>
       </c>
       <c r="B185" s="17" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="C185" s="9" t="s">
         <v>1020</v>
@@ -22637,7 +23964,7 @@
         <v>19</v>
       </c>
       <c r="F193" s="8" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="G193" s="7">
         <v>28</v>
@@ -22685,7 +24012,7 @@
         <v>19</v>
       </c>
       <c r="F194" s="3" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="G194" s="5">
         <v>152</v>
@@ -23249,7 +24576,7 @@
         <v>208</v>
       </c>
       <c r="B206" s="17" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="C206" s="9" t="s">
         <v>1130</v>
@@ -23633,7 +24960,7 @@
         <v>216</v>
       </c>
       <c r="B214" s="8" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="C214" s="9" t="s">
         <v>1173</v>
@@ -24497,7 +25824,7 @@
         <v>234</v>
       </c>
       <c r="B232" s="8" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="C232" s="9" t="s">
         <v>1245</v>
@@ -24641,7 +25968,7 @@
         <v>237</v>
       </c>
       <c r="B235" s="8" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="C235" s="9" t="s">
         <v>1259</v>
@@ -24881,7 +26208,7 @@
         <v>242</v>
       </c>
       <c r="B240" s="8" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="C240" s="9" t="s">
         <v>1284</v>
@@ -25805,7 +27132,7 @@
         <v>19</v>
       </c>
       <c r="F259" s="3" t="s">
-        <v>1386</v>
+        <v>1998</v>
       </c>
       <c r="G259" s="5">
         <v>125</v>
@@ -25817,13 +27144,13 @@
         <v>125</v>
       </c>
       <c r="J259" s="3" t="s">
+        <v>1386</v>
+      </c>
+      <c r="K259" s="3" t="s">
         <v>1387</v>
       </c>
-      <c r="K259" s="3" t="s">
+      <c r="L259" s="3" t="s">
         <v>1388</v>
-      </c>
-      <c r="L259" s="3" t="s">
-        <v>1389</v>
       </c>
       <c r="M259" s="3"/>
       <c r="N259" s="5">
@@ -25833,7 +27160,7 @@
         <v>126</v>
       </c>
       <c r="P259" s="3" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="260" spans="1:16" ht="12.75" customHeight="1">
@@ -25844,16 +27171,16 @@
         <v>31</v>
       </c>
       <c r="C260" s="6" t="s">
+        <v>1389</v>
+      </c>
+      <c r="D260" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E260" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F260" s="3" t="s">
         <v>1390</v>
-      </c>
-      <c r="D260" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E260" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F260" s="3" t="s">
-        <v>1391</v>
       </c>
       <c r="G260" s="5">
         <v>10</v>
@@ -25865,13 +27192,13 @@
         <v>10</v>
       </c>
       <c r="J260" s="3" t="s">
+        <v>1391</v>
+      </c>
+      <c r="K260" s="3" t="s">
         <v>1392</v>
       </c>
-      <c r="K260" s="3" t="s">
+      <c r="L260" s="3" t="s">
         <v>1393</v>
-      </c>
-      <c r="L260" s="3" t="s">
-        <v>1394</v>
       </c>
       <c r="M260" s="3"/>
       <c r="N260" s="5">
@@ -25881,7 +27208,7 @@
         <v>158</v>
       </c>
       <c r="P260" s="3" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="261" spans="1:16" ht="12.75" customHeight="1">
@@ -25889,11 +27216,11 @@
         <v>264</v>
       </c>
       <c r="B261" s="1" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C261" s="6" t="s">
         <v>1395</v>
       </c>
-      <c r="C261" s="6" t="s">
-        <v>1396</v>
-      </c>
       <c r="D261" s="3" t="s">
         <v>18</v>
       </c>
@@ -25901,7 +27228,7 @@
         <v>19</v>
       </c>
       <c r="F261" s="3" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="G261" s="5">
         <v>60</v>
@@ -25913,13 +27240,13 @@
         <v>60</v>
       </c>
       <c r="J261" s="3" t="s">
+        <v>1396</v>
+      </c>
+      <c r="K261" s="3" t="s">
         <v>1397</v>
       </c>
-      <c r="K261" s="3" t="s">
-        <v>1398</v>
-      </c>
       <c r="L261" s="3" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="M261" s="3"/>
       <c r="N261" s="5">
@@ -25929,7 +27256,7 @@
         <v>202</v>
       </c>
       <c r="P261" s="3" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="262" spans="1:16" ht="12.75" customHeight="1">
@@ -25937,11 +27264,11 @@
         <v>265</v>
       </c>
       <c r="B262" s="1" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C262" s="6" t="s">
         <v>1399</v>
       </c>
-      <c r="C262" s="6" t="s">
-        <v>1400</v>
-      </c>
       <c r="D262" s="3" t="s">
         <v>18</v>
       </c>
@@ -25949,7 +27276,7 @@
         <v>19</v>
       </c>
       <c r="F262" s="3" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="G262" s="5">
         <v>78</v>
@@ -25961,13 +27288,13 @@
         <v>78</v>
       </c>
       <c r="J262" s="3" t="s">
+        <v>1400</v>
+      </c>
+      <c r="K262" s="3" t="s">
         <v>1401</v>
       </c>
-      <c r="K262" s="3" t="s">
+      <c r="L262" s="3" t="s">
         <v>1402</v>
-      </c>
-      <c r="L262" s="3" t="s">
-        <v>1403</v>
       </c>
       <c r="M262" s="3"/>
       <c r="N262" s="5">
@@ -25977,7 +27304,7 @@
         <v>79</v>
       </c>
       <c r="P262" s="3" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="263" spans="1:16" ht="12.75" customHeight="1">
@@ -25985,11 +27312,11 @@
         <v>266</v>
       </c>
       <c r="B263" s="1" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C263" s="6" t="s">
         <v>1405</v>
       </c>
-      <c r="C263" s="6" t="s">
-        <v>1406</v>
-      </c>
       <c r="D263" s="3" t="s">
         <v>18</v>
       </c>
@@ -25997,7 +27324,7 @@
         <v>19</v>
       </c>
       <c r="F263" s="3" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="G263" s="5">
         <v>49</v>
@@ -26009,13 +27336,13 @@
         <v>192</v>
       </c>
       <c r="J263" s="3" t="s">
+        <v>1406</v>
+      </c>
+      <c r="K263" s="3" t="s">
         <v>1407</v>
       </c>
-      <c r="K263" s="3" t="s">
+      <c r="L263" s="3" t="s">
         <v>1408</v>
-      </c>
-      <c r="L263" s="3" t="s">
-        <v>1409</v>
       </c>
       <c r="M263" s="3"/>
       <c r="N263" s="5">
@@ -26025,7 +27352,7 @@
         <v>189</v>
       </c>
       <c r="P263" s="3" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="264" spans="1:16" ht="12.75" customHeight="1">
@@ -26033,11 +27360,11 @@
         <v>267</v>
       </c>
       <c r="B264" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C264" s="6" t="s">
         <v>1410</v>
       </c>
-      <c r="C264" s="6" t="s">
-        <v>1411</v>
-      </c>
       <c r="D264" s="3" t="s">
         <v>18</v>
       </c>
@@ -26045,7 +27372,7 @@
         <v>19</v>
       </c>
       <c r="F264" s="3" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="G264" s="5">
         <v>63</v>
@@ -26057,13 +27384,13 @@
         <v>206</v>
       </c>
       <c r="J264" s="3" t="s">
+        <v>1411</v>
+      </c>
+      <c r="K264" s="3" t="s">
         <v>1412</v>
       </c>
-      <c r="K264" s="3" t="s">
+      <c r="L264" s="3" t="s">
         <v>1413</v>
-      </c>
-      <c r="L264" s="3" t="s">
-        <v>1414</v>
       </c>
       <c r="M264" s="3"/>
       <c r="N264" s="5">
@@ -26073,7 +27400,7 @@
         <v>62</v>
       </c>
       <c r="P264" s="3" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="265" spans="1:16" ht="12.75" customHeight="1">
@@ -26084,7 +27411,7 @@
         <v>16</v>
       </c>
       <c r="C265" s="6" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="D265" s="3" t="s">
         <v>241</v>
@@ -26093,7 +27420,7 @@
         <v>19</v>
       </c>
       <c r="F265" s="3" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="G265" s="5">
         <v>34</v>
@@ -26105,13 +27432,13 @@
         <v>34</v>
       </c>
       <c r="J265" s="3" t="s">
+        <v>1417</v>
+      </c>
+      <c r="K265" s="3" t="s">
         <v>1418</v>
       </c>
-      <c r="K265" s="3" t="s">
+      <c r="L265" s="3" t="s">
         <v>1419</v>
-      </c>
-      <c r="L265" s="3" t="s">
-        <v>1420</v>
       </c>
       <c r="M265" s="3"/>
       <c r="N265" s="5">
@@ -26121,7 +27448,7 @@
         <v>35</v>
       </c>
       <c r="P265" s="3" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="266" spans="1:16" ht="12.75" customHeight="1">
@@ -26132,16 +27459,16 @@
         <v>1065</v>
       </c>
       <c r="C266" s="9" t="s">
+        <v>1421</v>
+      </c>
+      <c r="D266" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E266" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F266" s="8" t="s">
         <v>1422</v>
-      </c>
-      <c r="D266" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E266" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F266" s="8" t="s">
-        <v>1423</v>
       </c>
       <c r="G266" s="7">
         <v>33</v>
@@ -26153,13 +27480,13 @@
         <v>33</v>
       </c>
       <c r="J266" s="8" t="s">
+        <v>1423</v>
+      </c>
+      <c r="K266" s="8" t="s">
         <v>1424</v>
       </c>
-      <c r="K266" s="8" t="s">
+      <c r="L266" s="8" t="s">
         <v>1425</v>
-      </c>
-      <c r="L266" s="8" t="s">
-        <v>1426</v>
       </c>
       <c r="M266" s="3"/>
       <c r="N266" s="5">
@@ -26169,7 +27496,7 @@
         <v>168</v>
       </c>
       <c r="P266" s="3" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="267" spans="1:16" ht="12.75" customHeight="1">
@@ -26177,19 +27504,19 @@
         <v>270</v>
       </c>
       <c r="B267" s="1" t="s">
+        <v>1426</v>
+      </c>
+      <c r="C267" s="6" t="s">
         <v>1427</v>
       </c>
-      <c r="C267" s="6" t="s">
+      <c r="D267" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E267" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F267" s="3" t="s">
         <v>1428</v>
-      </c>
-      <c r="D267" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E267" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F267" s="3" t="s">
-        <v>1429</v>
       </c>
       <c r="G267" s="5">
         <v>3</v>
@@ -26201,13 +27528,13 @@
         <v>108</v>
       </c>
       <c r="J267" s="3" t="s">
+        <v>1429</v>
+      </c>
+      <c r="K267" s="3" t="s">
         <v>1430</v>
       </c>
-      <c r="K267" s="3" t="s">
+      <c r="L267" s="3" t="s">
         <v>1431</v>
-      </c>
-      <c r="L267" s="3" t="s">
-        <v>1432</v>
       </c>
       <c r="M267" s="3"/>
       <c r="N267" s="5">
@@ -26217,7 +27544,7 @@
         <v>109</v>
       </c>
       <c r="P267" s="3" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="268" spans="1:16" ht="12.75" customHeight="1">
@@ -26225,19 +27552,19 @@
         <v>271</v>
       </c>
       <c r="B268" s="1" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C268" s="6" t="s">
         <v>1433</v>
       </c>
-      <c r="C268" s="6" t="s">
+      <c r="D268" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E268" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F268" s="3" t="s">
         <v>1434</v>
-      </c>
-      <c r="D268" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E268" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F268" s="3" t="s">
-        <v>1435</v>
       </c>
       <c r="G268" s="5">
         <v>120</v>
@@ -26249,13 +27576,13 @@
         <v>120</v>
       </c>
       <c r="J268" s="3" t="s">
+        <v>1435</v>
+      </c>
+      <c r="K268" s="3" t="s">
         <v>1436</v>
       </c>
-      <c r="K268" s="3" t="s">
+      <c r="L268" s="3" t="s">
         <v>1437</v>
-      </c>
-      <c r="L268" s="3" t="s">
-        <v>1438</v>
       </c>
       <c r="M268" s="3"/>
       <c r="N268" s="5">
@@ -26265,7 +27592,7 @@
         <v>236</v>
       </c>
       <c r="P268" s="3" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="269" spans="1:16" ht="12.75" customHeight="1">
@@ -26273,11 +27600,11 @@
         <v>272</v>
       </c>
       <c r="B269" s="1" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C269" s="6" t="s">
         <v>1440</v>
       </c>
-      <c r="C269" s="6" t="s">
-        <v>1441</v>
-      </c>
       <c r="D269" s="3" t="s">
         <v>18</v>
       </c>
@@ -26285,7 +27612,7 @@
         <v>19</v>
       </c>
       <c r="F269" s="3" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="G269" s="5">
         <v>115</v>
@@ -26297,13 +27624,13 @@
         <v>234</v>
       </c>
       <c r="J269" s="3" t="s">
+        <v>1441</v>
+      </c>
+      <c r="K269" s="3" t="s">
         <v>1442</v>
       </c>
-      <c r="K269" s="3" t="s">
+      <c r="L269" s="3" t="s">
         <v>1443</v>
-      </c>
-      <c r="L269" s="3" t="s">
-        <v>1444</v>
       </c>
       <c r="M269" s="3"/>
       <c r="N269" s="5">
@@ -26313,7 +27640,7 @@
         <v>231</v>
       </c>
       <c r="P269" s="3" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="270" spans="1:16" ht="12.75" customHeight="1">
@@ -26321,19 +27648,19 @@
         <v>273</v>
       </c>
       <c r="B270" s="1" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C270" s="6" t="s">
         <v>1445</v>
       </c>
-      <c r="C270" s="6" t="s">
+      <c r="D270" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E270" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F270" s="3" t="s">
         <v>1446</v>
-      </c>
-      <c r="D270" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E270" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F270" s="3" t="s">
-        <v>1447</v>
       </c>
       <c r="G270" s="5">
         <v>60</v>
@@ -26345,13 +27672,13 @@
         <v>60</v>
       </c>
       <c r="J270" s="3" t="s">
+        <v>1447</v>
+      </c>
+      <c r="K270" s="3" t="s">
         <v>1448</v>
       </c>
-      <c r="K270" s="3" t="s">
+      <c r="L270" s="3" t="s">
         <v>1449</v>
-      </c>
-      <c r="L270" s="3" t="s">
-        <v>1450</v>
       </c>
       <c r="M270" s="3"/>
       <c r="N270" s="5">
@@ -26361,7 +27688,7 @@
         <v>137</v>
       </c>
       <c r="P270" s="3" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="271" spans="1:16" ht="12.75" customHeight="1">
@@ -26369,11 +27696,11 @@
         <v>274</v>
       </c>
       <c r="B271" s="1" t="s">
+        <v>1450</v>
+      </c>
+      <c r="C271" s="6" t="s">
         <v>1451</v>
       </c>
-      <c r="C271" s="6" t="s">
-        <v>1452</v>
-      </c>
       <c r="D271" s="3" t="s">
         <v>18</v>
       </c>
@@ -26381,7 +27708,7 @@
         <v>19</v>
       </c>
       <c r="F271" s="3" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="G271" s="5">
         <v>79</v>
@@ -26393,13 +27720,13 @@
         <v>79</v>
       </c>
       <c r="J271" s="3" t="s">
+        <v>1452</v>
+      </c>
+      <c r="K271" s="3" t="s">
         <v>1453</v>
       </c>
-      <c r="K271" s="3" t="s">
+      <c r="L271" s="3" t="s">
         <v>1454</v>
-      </c>
-      <c r="L271" s="3" t="s">
-        <v>1455</v>
       </c>
       <c r="M271" s="3"/>
       <c r="N271" s="5">
@@ -26409,7 +27736,7 @@
         <v>156</v>
       </c>
       <c r="P271" s="3" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="272" spans="1:16" ht="12.75" customHeight="1">
@@ -26417,19 +27744,19 @@
         <v>275</v>
       </c>
       <c r="B272" s="1" t="s">
+        <v>1455</v>
+      </c>
+      <c r="C272" s="6" t="s">
         <v>1456</v>
       </c>
-      <c r="C272" s="6" t="s">
+      <c r="D272" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E272" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F272" s="3" t="s">
         <v>1457</v>
-      </c>
-      <c r="D272" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E272" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F272" s="3" t="s">
-        <v>1458</v>
       </c>
       <c r="G272" s="5">
         <v>53</v>
@@ -26441,13 +27768,13 @@
         <v>53</v>
       </c>
       <c r="J272" s="3" t="s">
+        <v>1458</v>
+      </c>
+      <c r="K272" s="3" t="s">
         <v>1459</v>
       </c>
-      <c r="K272" s="3" t="s">
+      <c r="L272" s="3" t="s">
         <v>1460</v>
-      </c>
-      <c r="L272" s="3" t="s">
-        <v>1461</v>
       </c>
       <c r="M272" s="3"/>
       <c r="N272" s="5">
@@ -26457,7 +27784,7 @@
         <v>148</v>
       </c>
       <c r="P272" s="3" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="273" spans="1:16" ht="12.75" customHeight="1">
@@ -26465,11 +27792,11 @@
         <v>276</v>
       </c>
       <c r="B273" s="1" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C273" s="6" t="s">
         <v>1463</v>
       </c>
-      <c r="C273" s="6" t="s">
-        <v>1464</v>
-      </c>
       <c r="D273" s="3" t="s">
         <v>18</v>
       </c>
@@ -26477,7 +27804,7 @@
         <v>19</v>
       </c>
       <c r="F273" s="3" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="G273" s="5">
         <v>87</v>
@@ -26489,13 +27816,13 @@
         <v>87</v>
       </c>
       <c r="J273" s="3" t="s">
+        <v>1464</v>
+      </c>
+      <c r="K273" s="3" t="s">
         <v>1465</v>
       </c>
-      <c r="K273" s="3" t="s">
+      <c r="L273" s="3" t="s">
         <v>1466</v>
-      </c>
-      <c r="L273" s="3" t="s">
-        <v>1467</v>
       </c>
       <c r="M273" s="3"/>
       <c r="N273" s="5">
@@ -26505,7 +27832,7 @@
         <v>177</v>
       </c>
       <c r="P273" s="3" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="274" spans="1:16" ht="12.75" customHeight="1">
@@ -26513,19 +27840,19 @@
         <v>277</v>
       </c>
       <c r="B274" s="1" t="s">
+        <v>1467</v>
+      </c>
+      <c r="C274" s="6" t="s">
         <v>1468</v>
       </c>
-      <c r="C274" s="6" t="s">
+      <c r="D274" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E274" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F274" s="3" t="s">
         <v>1469</v>
-      </c>
-      <c r="D274" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E274" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F274" s="3" t="s">
-        <v>1470</v>
       </c>
       <c r="G274" s="5">
         <v>121</v>
@@ -26537,13 +27864,13 @@
         <v>121</v>
       </c>
       <c r="J274" s="3" t="s">
+        <v>1470</v>
+      </c>
+      <c r="K274" s="3" t="s">
         <v>1471</v>
       </c>
-      <c r="K274" s="3" t="s">
+      <c r="L274" s="3" t="s">
         <v>1472</v>
-      </c>
-      <c r="L274" s="3" t="s">
-        <v>1473</v>
       </c>
       <c r="M274" s="3"/>
       <c r="N274" s="5">
@@ -26553,7 +27880,7 @@
         <v>264</v>
       </c>
       <c r="P274" s="3" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="275" spans="1:16" ht="12.75" customHeight="1">
@@ -26561,19 +27888,19 @@
         <v>278</v>
       </c>
       <c r="B275" s="1" t="s">
+        <v>1474</v>
+      </c>
+      <c r="C275" s="6" t="s">
         <v>1475</v>
       </c>
-      <c r="C275" s="6" t="s">
+      <c r="D275" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E275" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F275" s="3" t="s">
         <v>1476</v>
-      </c>
-      <c r="D275" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E275" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F275" s="3" t="s">
-        <v>1477</v>
       </c>
       <c r="G275" s="5">
         <v>4</v>
@@ -26585,13 +27912,13 @@
         <v>4</v>
       </c>
       <c r="J275" s="3" t="s">
+        <v>1477</v>
+      </c>
+      <c r="K275" s="3" t="s">
         <v>1478</v>
       </c>
-      <c r="K275" s="3" t="s">
+      <c r="L275" s="3" t="s">
         <v>1479</v>
-      </c>
-      <c r="L275" s="3" t="s">
-        <v>1480</v>
       </c>
       <c r="M275" s="3"/>
       <c r="N275" s="5">
@@ -26601,7 +27928,7 @@
         <v>139</v>
       </c>
       <c r="P275" s="3" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="276" spans="1:16" ht="12.75" customHeight="1">
@@ -26609,19 +27936,19 @@
         <v>279</v>
       </c>
       <c r="B276" s="1" t="s">
+        <v>1480</v>
+      </c>
+      <c r="C276" s="6" t="s">
         <v>1481</v>
       </c>
-      <c r="C276" s="6" t="s">
+      <c r="D276" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E276" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F276" s="3" t="s">
         <v>1482</v>
-      </c>
-      <c r="D276" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E276" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F276" s="3" t="s">
-        <v>1483</v>
       </c>
       <c r="G276" s="5">
         <v>75</v>
@@ -26633,10 +27960,10 @@
         <v>75</v>
       </c>
       <c r="J276" s="3" t="s">
+        <v>1483</v>
+      </c>
+      <c r="K276" s="3" t="s">
         <v>1484</v>
-      </c>
-      <c r="K276" s="3" t="s">
-        <v>1485</v>
       </c>
       <c r="L276" s="3" t="s">
         <v>924</v>
@@ -26649,7 +27976,7 @@
         <v>76</v>
       </c>
       <c r="P276" s="3" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="277" spans="1:16" ht="12.75" customHeight="1">
@@ -26657,19 +27984,19 @@
         <v>280</v>
       </c>
       <c r="B277" s="1" t="s">
+        <v>1486</v>
+      </c>
+      <c r="C277" s="6" t="s">
         <v>1487</v>
       </c>
-      <c r="C277" s="6" t="s">
+      <c r="D277" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E277" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F277" s="3" t="s">
         <v>1488</v>
-      </c>
-      <c r="D277" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E277" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F277" s="3" t="s">
-        <v>1489</v>
       </c>
       <c r="G277" s="5">
         <v>106</v>
@@ -26681,13 +28008,13 @@
         <v>106</v>
       </c>
       <c r="J277" s="3" t="s">
+        <v>1489</v>
+      </c>
+      <c r="K277" s="3" t="s">
         <v>1490</v>
       </c>
-      <c r="K277" s="3" t="s">
+      <c r="L277" s="3" t="s">
         <v>1491</v>
-      </c>
-      <c r="L277" s="3" t="s">
-        <v>1492</v>
       </c>
       <c r="M277" s="3"/>
       <c r="N277" s="5">
@@ -26697,7 +28024,7 @@
         <v>107</v>
       </c>
       <c r="P277" s="3" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="278" spans="1:16" ht="12.75" customHeight="1">
@@ -26708,7 +28035,7 @@
         <v>350</v>
       </c>
       <c r="C278" s="6" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="D278" s="3" t="s">
         <v>18</v>
@@ -26717,7 +28044,7 @@
         <v>19</v>
       </c>
       <c r="F278" s="3" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="G278" s="5">
         <v>113</v>
@@ -26729,13 +28056,13 @@
         <v>256</v>
       </c>
       <c r="J278" s="3" t="s">
+        <v>1494</v>
+      </c>
+      <c r="K278" s="3" t="s">
         <v>1495</v>
       </c>
-      <c r="K278" s="3" t="s">
+      <c r="L278" s="3" t="s">
         <v>1496</v>
-      </c>
-      <c r="L278" s="3" t="s">
-        <v>1497</v>
       </c>
       <c r="M278" s="3"/>
       <c r="N278" s="5">
@@ -26745,7 +28072,7 @@
         <v>114</v>
       </c>
       <c r="P278" s="3" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="279" spans="1:16" ht="12.75" customHeight="1">
@@ -26753,19 +28080,19 @@
         <v>282</v>
       </c>
       <c r="B279" s="1" t="s">
+        <v>1497</v>
+      </c>
+      <c r="C279" s="6" t="s">
         <v>1498</v>
       </c>
-      <c r="C279" s="6" t="s">
+      <c r="D279" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E279" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F279" s="3" t="s">
         <v>1499</v>
-      </c>
-      <c r="D279" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E279" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F279" s="3" t="s">
-        <v>1500</v>
       </c>
       <c r="G279" s="5">
         <v>99</v>
@@ -26777,13 +28104,13 @@
         <v>99</v>
       </c>
       <c r="J279" s="3" t="s">
+        <v>1500</v>
+      </c>
+      <c r="K279" s="3" t="s">
         <v>1501</v>
       </c>
-      <c r="K279" s="3" t="s">
-        <v>1502</v>
-      </c>
       <c r="L279" s="3" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="M279" s="3"/>
       <c r="N279" s="5">
@@ -26793,7 +28120,7 @@
         <v>100</v>
       </c>
       <c r="P279" s="3" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="280" spans="1:16" ht="12.75" customHeight="1">
@@ -26804,16 +28131,16 @@
         <v>31</v>
       </c>
       <c r="C280" s="3" t="s">
+        <v>1516</v>
+      </c>
+      <c r="D280" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E280" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F280" s="3" t="s">
         <v>1517</v>
-      </c>
-      <c r="D280" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E280" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F280" s="3" t="s">
-        <v>1518</v>
       </c>
       <c r="G280" s="3">
         <v>146</v>
@@ -26825,13 +28152,13 @@
         <v>146</v>
       </c>
       <c r="J280" s="3" t="s">
+        <v>1518</v>
+      </c>
+      <c r="K280" s="3" t="s">
         <v>1519</v>
       </c>
-      <c r="K280" s="3" t="s">
+      <c r="L280" s="3" t="s">
         <v>1520</v>
-      </c>
-      <c r="L280" s="3" t="s">
-        <v>1521</v>
       </c>
       <c r="M280" s="3"/>
       <c r="N280" s="3">
@@ -26841,7 +28168,7 @@
         <v>147</v>
       </c>
       <c r="P280" s="3" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="281" spans="1:16" ht="12.75" customHeight="1">
@@ -26849,10 +28176,10 @@
         <v>284</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="D281" s="3" t="s">
         <v>18</v>
@@ -26861,7 +28188,7 @@
         <v>19</v>
       </c>
       <c r="F281" s="3" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="G281" s="3">
         <v>153</v>
@@ -26873,13 +28200,13 @@
         <v>298</v>
       </c>
       <c r="J281" s="3" t="s">
+        <v>1523</v>
+      </c>
+      <c r="K281" s="3" t="s">
         <v>1524</v>
       </c>
-      <c r="K281" s="3" t="s">
+      <c r="L281" s="3" t="s">
         <v>1525</v>
-      </c>
-      <c r="L281" s="3" t="s">
-        <v>1526</v>
       </c>
       <c r="M281" s="3"/>
       <c r="N281" s="3">
@@ -26889,7 +28216,7 @@
         <v>159</v>
       </c>
       <c r="P281" s="3" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="282" spans="1:16" ht="12.75" customHeight="1">
@@ -26897,19 +28224,19 @@
         <v>285</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="C282" s="3" t="s">
+        <v>1526</v>
+      </c>
+      <c r="D282" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E282" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F282" s="3" t="s">
         <v>1527</v>
-      </c>
-      <c r="D282" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E282" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F282" s="3" t="s">
-        <v>1528</v>
       </c>
       <c r="G282" s="3">
         <v>10</v>
@@ -26921,13 +28248,13 @@
         <v>10</v>
       </c>
       <c r="J282" s="3" t="s">
+        <v>1528</v>
+      </c>
+      <c r="K282" s="3" t="s">
         <v>1529</v>
       </c>
-      <c r="K282" s="3" t="s">
+      <c r="L282" s="3" t="s">
         <v>1530</v>
-      </c>
-      <c r="L282" s="3" t="s">
-        <v>1531</v>
       </c>
       <c r="M282" s="3"/>
       <c r="N282" s="3">
@@ -26937,7 +28264,7 @@
         <v>181</v>
       </c>
       <c r="P282" s="3" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="283" spans="1:16" ht="12.75" customHeight="1">
@@ -26948,16 +28275,16 @@
         <v>479</v>
       </c>
       <c r="C283" s="3" t="s">
+        <v>1531</v>
+      </c>
+      <c r="D283" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E283" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F283" s="3" t="s">
         <v>1532</v>
-      </c>
-      <c r="D283" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E283" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F283" s="3" t="s">
-        <v>1533</v>
       </c>
       <c r="G283" s="3">
         <v>33</v>
@@ -26969,13 +28296,13 @@
         <v>33</v>
       </c>
       <c r="J283" s="3" t="s">
+        <v>1533</v>
+      </c>
+      <c r="K283" s="3" t="s">
         <v>1534</v>
       </c>
-      <c r="K283" s="3" t="s">
+      <c r="L283" s="3" t="s">
         <v>1535</v>
-      </c>
-      <c r="L283" s="3" t="s">
-        <v>1536</v>
       </c>
       <c r="M283" s="3"/>
       <c r="N283" s="3">
@@ -26985,7 +28312,7 @@
         <v>34</v>
       </c>
       <c r="P283" s="3" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="284" spans="1:16" ht="12.75" customHeight="1">
@@ -26993,10 +28320,10 @@
         <v>287</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="C284" s="3" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="D284" s="3" t="s">
         <v>18</v>
@@ -27005,7 +28332,7 @@
         <v>19</v>
       </c>
       <c r="F284" s="3" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="G284" s="3">
         <v>7</v>
@@ -27017,13 +28344,13 @@
         <v>165</v>
       </c>
       <c r="J284" s="3" t="s">
+        <v>1538</v>
+      </c>
+      <c r="K284" s="3" t="s">
         <v>1539</v>
       </c>
-      <c r="K284" s="3" t="s">
+      <c r="L284" s="3" t="s">
         <v>1540</v>
-      </c>
-      <c r="L284" s="3" t="s">
-        <v>1541</v>
       </c>
       <c r="M284" s="3"/>
       <c r="N284" s="3">
@@ -27033,7 +28360,7 @@
         <v>154</v>
       </c>
       <c r="P284" s="3" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="285" spans="1:16" ht="12.75" customHeight="1">
@@ -27041,10 +28368,10 @@
         <v>288</v>
       </c>
       <c r="B285" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="C285" s="3" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="D285" s="3" t="s">
         <v>18</v>
@@ -27065,13 +28392,13 @@
         <v>69</v>
       </c>
       <c r="J285" s="3" t="s">
+        <v>1542</v>
+      </c>
+      <c r="K285" s="3" t="s">
         <v>1543</v>
       </c>
-      <c r="K285" s="3" t="s">
+      <c r="L285" s="3" t="s">
         <v>1544</v>
-      </c>
-      <c r="L285" s="3" t="s">
-        <v>1545</v>
       </c>
       <c r="M285" s="3"/>
       <c r="N285" s="3">
@@ -27081,7 +28408,7 @@
         <v>225</v>
       </c>
       <c r="P285" s="3" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="286" spans="1:16" ht="12.75" customHeight="1">
@@ -27092,7 +28419,7 @@
         <v>16</v>
       </c>
       <c r="C286" s="8" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="D286" s="8" t="s">
         <v>18</v>
@@ -27137,19 +28464,19 @@
         <v>290</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="C287" s="3" t="s">
+        <v>1547</v>
+      </c>
+      <c r="D287" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E287" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F287" s="3" t="s">
         <v>1548</v>
-      </c>
-      <c r="D287" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E287" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F287" s="3" t="s">
-        <v>1549</v>
       </c>
       <c r="G287" s="3">
         <v>102</v>
@@ -27161,13 +28488,13 @@
         <v>201</v>
       </c>
       <c r="J287" s="3" t="s">
+        <v>1549</v>
+      </c>
+      <c r="K287" s="3" t="s">
         <v>1550</v>
       </c>
-      <c r="K287" s="3" t="s">
+      <c r="L287" s="3" t="s">
         <v>1551</v>
-      </c>
-      <c r="L287" s="3" t="s">
-        <v>1552</v>
       </c>
       <c r="M287" s="3"/>
       <c r="N287" s="3">
@@ -27177,7 +28504,7 @@
         <v>110</v>
       </c>
       <c r="P287" s="3" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="288" spans="1:16" ht="12.75" customHeight="1">
@@ -27185,10 +28512,10 @@
         <v>291</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="C288" s="3" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="D288" s="3" t="s">
         <v>18</v>
@@ -27197,7 +28524,7 @@
         <v>19</v>
       </c>
       <c r="F288" s="3" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="G288" s="3">
         <v>6</v>
@@ -27209,13 +28536,13 @@
         <v>45450</v>
       </c>
       <c r="J288" s="3" t="s">
+        <v>1554</v>
+      </c>
+      <c r="K288" s="3" t="s">
         <v>1555</v>
       </c>
-      <c r="K288" s="3" t="s">
+      <c r="L288" s="3" t="s">
         <v>1556</v>
-      </c>
-      <c r="L288" s="3" t="s">
-        <v>1557</v>
       </c>
       <c r="M288" s="3"/>
       <c r="N288" s="3">
@@ -27225,7 +28552,7 @@
         <v>7</v>
       </c>
       <c r="P288" s="3" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="289" spans="1:16" ht="12.75" customHeight="1">
@@ -27233,19 +28560,19 @@
         <v>292</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="C289" s="3" t="s">
+        <v>1557</v>
+      </c>
+      <c r="D289" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E289" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F289" s="3" t="s">
         <v>1558</v>
-      </c>
-      <c r="D289" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E289" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F289" s="3" t="s">
-        <v>1559</v>
       </c>
       <c r="G289" s="3">
         <v>88</v>
@@ -27257,13 +28584,13 @@
         <v>140</v>
       </c>
       <c r="J289" s="3" t="s">
+        <v>1559</v>
+      </c>
+      <c r="K289" s="3" t="s">
         <v>1560</v>
       </c>
-      <c r="K289" s="3" t="s">
+      <c r="L289" s="3" t="s">
         <v>1561</v>
-      </c>
-      <c r="L289" s="3" t="s">
-        <v>1562</v>
       </c>
       <c r="M289" s="3"/>
       <c r="N289" s="3">
@@ -27273,7 +28600,7 @@
         <v>182</v>
       </c>
       <c r="P289" s="3" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="290" spans="1:16" ht="12.75" customHeight="1">
@@ -27281,19 +28608,19 @@
         <v>293</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="C290" s="3" t="s">
+        <v>1563</v>
+      </c>
+      <c r="D290" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E290" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F290" s="3" t="s">
         <v>1564</v>
-      </c>
-      <c r="D290" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E290" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F290" s="3" t="s">
-        <v>1565</v>
       </c>
       <c r="G290" s="3">
         <v>102</v>
@@ -27305,13 +28632,13 @@
         <v>102</v>
       </c>
       <c r="J290" s="3" t="s">
+        <v>1565</v>
+      </c>
+      <c r="K290" s="3" t="s">
         <v>1566</v>
       </c>
-      <c r="K290" s="3" t="s">
+      <c r="L290" s="3" t="s">
         <v>1567</v>
-      </c>
-      <c r="L290" s="3" t="s">
-        <v>1568</v>
       </c>
       <c r="M290" s="3"/>
       <c r="N290" s="3">
@@ -27321,7 +28648,7 @@
         <v>302</v>
       </c>
       <c r="P290" s="3" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="291" spans="1:16" ht="12.75" customHeight="1">
@@ -27329,19 +28656,19 @@
         <v>294</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="C291" s="3" t="s">
+        <v>1569</v>
+      </c>
+      <c r="D291" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E291" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F291" s="3" t="s">
         <v>1570</v>
-      </c>
-      <c r="D291" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E291" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F291" s="3" t="s">
-        <v>1571</v>
       </c>
       <c r="G291" s="3">
         <v>91</v>
@@ -27353,13 +28680,13 @@
         <v>91</v>
       </c>
       <c r="J291" s="3" t="s">
+        <v>1571</v>
+      </c>
+      <c r="K291" s="3" t="s">
         <v>1572</v>
       </c>
-      <c r="K291" s="3" t="s">
+      <c r="L291" s="3" t="s">
         <v>1573</v>
-      </c>
-      <c r="L291" s="3" t="s">
-        <v>1574</v>
       </c>
       <c r="M291" s="3"/>
       <c r="N291" s="3">
@@ -27369,7 +28696,7 @@
         <v>90</v>
       </c>
       <c r="P291" s="3" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="292" spans="1:16" ht="12.75" customHeight="1">
@@ -27377,10 +28704,10 @@
         <v>295</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="C292" s="3" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="D292" s="3" t="s">
         <v>18</v>
@@ -27389,7 +28716,7 @@
         <v>19</v>
       </c>
       <c r="F292" s="3" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="G292" s="3">
         <v>6</v>
@@ -27401,13 +28728,13 @@
         <v>119</v>
       </c>
       <c r="J292" s="3" t="s">
+        <v>1575</v>
+      </c>
+      <c r="K292" s="3" t="s">
         <v>1576</v>
       </c>
-      <c r="K292" s="3" t="s">
+      <c r="L292" s="3" t="s">
         <v>1577</v>
-      </c>
-      <c r="L292" s="3" t="s">
-        <v>1578</v>
       </c>
       <c r="M292" s="3"/>
       <c r="N292" s="3">
@@ -27417,7 +28744,7 @@
         <v>120</v>
       </c>
       <c r="P292" s="3" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="293" spans="1:16" ht="12.75" customHeight="1">
@@ -27428,16 +28755,16 @@
         <v>16</v>
       </c>
       <c r="C293" s="3" t="s">
+        <v>1578</v>
+      </c>
+      <c r="D293" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E293" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F293" s="3" t="s">
         <v>1579</v>
-      </c>
-      <c r="D293" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E293" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F293" s="3" t="s">
-        <v>1580</v>
       </c>
       <c r="G293" s="3">
         <v>84</v>
@@ -27449,13 +28776,13 @@
         <v>84</v>
       </c>
       <c r="J293" s="3" t="s">
+        <v>1580</v>
+      </c>
+      <c r="K293" s="3" t="s">
         <v>1581</v>
       </c>
-      <c r="K293" s="3" t="s">
+      <c r="L293" s="3" t="s">
         <v>1582</v>
-      </c>
-      <c r="L293" s="3" t="s">
-        <v>1583</v>
       </c>
       <c r="M293" s="3"/>
       <c r="N293" s="3">
@@ -27465,7 +28792,7 @@
         <v>201</v>
       </c>
       <c r="P293" s="3" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="294" spans="1:16" ht="12.75" customHeight="1">
@@ -27473,10 +28800,10 @@
         <v>297</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="C294" s="3" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="D294" s="3" t="s">
         <v>18</v>
@@ -27485,7 +28812,7 @@
         <v>19</v>
       </c>
       <c r="F294" s="3" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="G294" s="3">
         <v>110</v>
@@ -27497,13 +28824,13 @@
         <v>197</v>
       </c>
       <c r="J294" s="3" t="s">
+        <v>1584</v>
+      </c>
+      <c r="K294" s="3" t="s">
         <v>1585</v>
       </c>
-      <c r="K294" s="3" t="s">
+      <c r="L294" s="3" t="s">
         <v>1586</v>
-      </c>
-      <c r="L294" s="3" t="s">
-        <v>1587</v>
       </c>
       <c r="M294" s="3"/>
       <c r="N294" s="3">
@@ -27513,7 +28840,7 @@
         <v>114</v>
       </c>
       <c r="P294" s="3" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="295" spans="1:16" ht="12.75" customHeight="1">
@@ -27524,16 +28851,16 @@
         <v>16</v>
       </c>
       <c r="C295" s="3" t="s">
+        <v>1587</v>
+      </c>
+      <c r="D295" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E295" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F295" s="3" t="s">
         <v>1588</v>
-      </c>
-      <c r="D295" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E295" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F295" s="3" t="s">
-        <v>1589</v>
       </c>
       <c r="G295" s="3">
         <v>133</v>
@@ -27545,13 +28872,13 @@
         <v>283</v>
       </c>
       <c r="J295" s="3" t="s">
+        <v>1589</v>
+      </c>
+      <c r="K295" s="3" t="s">
         <v>1590</v>
       </c>
-      <c r="K295" s="3" t="s">
+      <c r="L295" s="3" t="s">
         <v>1591</v>
-      </c>
-      <c r="L295" s="3" t="s">
-        <v>1592</v>
       </c>
       <c r="M295" s="3"/>
       <c r="N295" s="3">
@@ -27561,7 +28888,7 @@
         <v>134</v>
       </c>
       <c r="P295" s="3" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="296" spans="1:16" ht="12.75" customHeight="1">
@@ -27572,7 +28899,7 @@
         <v>16</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="D296" s="3" t="s">
         <v>18</v>
@@ -27581,7 +28908,7 @@
         <v>19</v>
       </c>
       <c r="F296" s="3" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="G296" s="3">
         <v>136</v>
@@ -27593,13 +28920,13 @@
         <v>287</v>
       </c>
       <c r="J296" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="K296" s="3" t="s">
         <v>1595</v>
       </c>
-      <c r="K296" s="3" t="s">
-        <v>1596</v>
-      </c>
       <c r="L296" s="3" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="M296" s="3"/>
       <c r="N296" s="3">
@@ -27609,7 +28936,7 @@
         <v>137</v>
       </c>
       <c r="P296" s="3" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="297" spans="1:16" ht="12.75" customHeight="1">
@@ -27617,19 +28944,19 @@
         <v>300</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="C297" s="3" t="s">
+        <v>1596</v>
+      </c>
+      <c r="D297" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E297" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F297" s="3" t="s">
         <v>1597</v>
-      </c>
-      <c r="D297" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E297" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F297" s="3" t="s">
-        <v>1598</v>
       </c>
       <c r="G297" s="3">
         <v>81</v>
@@ -27641,13 +28968,13 @@
         <v>81</v>
       </c>
       <c r="J297" s="3" t="s">
+        <v>1598</v>
+      </c>
+      <c r="K297" s="3" t="s">
         <v>1599</v>
       </c>
-      <c r="K297" s="3" t="s">
+      <c r="L297" s="3" t="s">
         <v>1600</v>
-      </c>
-      <c r="L297" s="3" t="s">
-        <v>1601</v>
       </c>
       <c r="M297" s="3"/>
       <c r="N297" s="3">
@@ -27657,7 +28984,7 @@
         <v>242</v>
       </c>
       <c r="P297" s="3" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="298" spans="1:16" ht="12.75" customHeight="1">
@@ -27665,10 +28992,10 @@
         <v>301</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="C298" s="3" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="D298" s="3" t="s">
         <v>18</v>
@@ -27677,7 +29004,7 @@
         <v>19</v>
       </c>
       <c r="F298" s="3" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="G298" s="3">
         <v>152</v>
@@ -27689,13 +29016,13 @@
         <v>152</v>
       </c>
       <c r="J298" s="3" t="s">
+        <v>1602</v>
+      </c>
+      <c r="K298" s="3" t="s">
         <v>1603</v>
       </c>
-      <c r="K298" s="3" t="s">
+      <c r="L298" s="3" t="s">
         <v>1604</v>
-      </c>
-      <c r="L298" s="3" t="s">
-        <v>1605</v>
       </c>
       <c r="M298" s="3"/>
       <c r="N298" s="3">
@@ -27705,7 +29032,7 @@
         <v>312</v>
       </c>
       <c r="P298" s="3" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="299" spans="1:16" ht="12.75" customHeight="1">
@@ -27716,7 +29043,7 @@
         <v>16</v>
       </c>
       <c r="C299" s="3" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="D299" s="3" t="s">
         <v>18</v>
@@ -27725,7 +29052,7 @@
         <v>19</v>
       </c>
       <c r="F299" s="3" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="G299" s="3">
         <v>67</v>
@@ -27737,13 +29064,13 @@
         <v>228</v>
       </c>
       <c r="J299" s="3" t="s">
+        <v>1607</v>
+      </c>
+      <c r="K299" s="3" t="s">
         <v>1608</v>
       </c>
-      <c r="K299" s="3" t="s">
+      <c r="L299" s="3" t="s">
         <v>1609</v>
-      </c>
-      <c r="L299" s="3" t="s">
-        <v>1610</v>
       </c>
       <c r="M299" s="3"/>
       <c r="N299" s="3">
@@ -27753,7 +29080,7 @@
         <v>229</v>
       </c>
       <c r="P299" s="3" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="300" spans="1:16" ht="12.75" customHeight="1">
@@ -27764,7 +29091,7 @@
         <v>326</v>
       </c>
       <c r="C300" s="3" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="D300" s="3" t="s">
         <v>18</v>
@@ -27773,7 +29100,7 @@
         <v>19</v>
       </c>
       <c r="F300" s="3" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="G300" s="3">
         <v>86</v>
@@ -27785,13 +29112,13 @@
         <v>245</v>
       </c>
       <c r="J300" s="3" t="s">
+        <v>1611</v>
+      </c>
+      <c r="K300" s="3" t="s">
         <v>1612</v>
       </c>
-      <c r="K300" s="3" t="s">
+      <c r="L300" s="3" t="s">
         <v>1613</v>
-      </c>
-      <c r="L300" s="3" t="s">
-        <v>1614</v>
       </c>
       <c r="M300" s="3"/>
       <c r="N300" s="3">
@@ -27801,7 +29128,7 @@
         <v>246</v>
       </c>
       <c r="P300" s="3" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="301" spans="1:16" ht="12.75" customHeight="1">
@@ -27809,19 +29136,19 @@
         <v>304</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="C301" s="3" t="s">
+        <v>1614</v>
+      </c>
+      <c r="D301" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E301" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F301" s="3" t="s">
         <v>1615</v>
-      </c>
-      <c r="D301" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E301" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F301" s="3" t="s">
-        <v>1616</v>
       </c>
       <c r="G301" s="3">
         <v>2</v>
@@ -27833,13 +29160,13 @@
         <v>198</v>
       </c>
       <c r="J301" s="3" t="s">
+        <v>1616</v>
+      </c>
+      <c r="K301" s="3" t="s">
         <v>1617</v>
       </c>
-      <c r="K301" s="3" t="s">
+      <c r="L301" s="3" t="s">
         <v>1618</v>
-      </c>
-      <c r="L301" s="3" t="s">
-        <v>1619</v>
       </c>
       <c r="M301" s="3"/>
       <c r="N301" s="3">
@@ -27849,7 +29176,7 @@
         <v>199</v>
       </c>
       <c r="P301" s="3" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="302" spans="1:16" ht="12.75" customHeight="1">
@@ -27857,10 +29184,10 @@
         <v>305</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="C302" s="3" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="D302" s="3" t="s">
         <v>18</v>
@@ -27869,7 +29196,7 @@
         <v>19</v>
       </c>
       <c r="F302" s="3" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="G302" s="3">
         <v>193</v>
@@ -27881,13 +29208,13 @@
         <v>382</v>
       </c>
       <c r="J302" s="3" t="s">
+        <v>1620</v>
+      </c>
+      <c r="K302" s="3" t="s">
         <v>1621</v>
       </c>
-      <c r="K302" s="3" t="s">
+      <c r="L302" s="3" t="s">
         <v>1622</v>
-      </c>
-      <c r="L302" s="3" t="s">
-        <v>1623</v>
       </c>
       <c r="M302" s="3"/>
       <c r="N302" s="3">
@@ -27897,7 +29224,7 @@
         <v>204</v>
       </c>
       <c r="P302" s="3" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="303" spans="1:16" ht="12.75" customHeight="1">
@@ -27905,19 +29232,19 @@
         <v>306</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="C303" s="3" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D303" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E303" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F303" s="3" t="s">
         <v>1625</v>
-      </c>
-      <c r="D303" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E303" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F303" s="3" t="s">
-        <v>1626</v>
       </c>
       <c r="G303" s="3">
         <v>51</v>
@@ -27929,13 +29256,13 @@
         <v>51</v>
       </c>
       <c r="J303" s="3" t="s">
+        <v>1626</v>
+      </c>
+      <c r="K303" s="3" t="s">
         <v>1627</v>
       </c>
-      <c r="K303" s="3" t="s">
+      <c r="L303" s="3" t="s">
         <v>1628</v>
-      </c>
-      <c r="L303" s="3" t="s">
-        <v>1629</v>
       </c>
       <c r="M303" s="3"/>
       <c r="N303" s="3">
@@ -27945,7 +29272,7 @@
         <v>52</v>
       </c>
       <c r="P303" s="3" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="304" spans="1:16" ht="12.75" customHeight="1">
@@ -27956,7 +29283,7 @@
         <v>350</v>
       </c>
       <c r="C304" s="3" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="D304" s="3" t="s">
         <v>18</v>
@@ -27965,7 +29292,7 @@
         <v>19</v>
       </c>
       <c r="F304" s="3" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="G304" s="3">
         <v>89</v>
@@ -27977,13 +29304,13 @@
         <v>89</v>
       </c>
       <c r="J304" s="3" t="s">
+        <v>1630</v>
+      </c>
+      <c r="K304" s="3" t="s">
         <v>1631</v>
       </c>
-      <c r="K304" s="3" t="s">
+      <c r="L304" s="3" t="s">
         <v>1632</v>
-      </c>
-      <c r="L304" s="3" t="s">
-        <v>1633</v>
       </c>
       <c r="M304" s="3"/>
       <c r="N304" s="3">
@@ -27993,7 +29320,7 @@
         <v>90</v>
       </c>
       <c r="P304" s="3" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="305" spans="1:16" ht="12.75" customHeight="1">
@@ -28004,7 +29331,7 @@
         <v>16</v>
       </c>
       <c r="C305" s="3" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="D305" s="3" t="s">
         <v>18</v>
@@ -28049,19 +29376,19 @@
         <v>309</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="C306" s="3" t="s">
+        <v>1634</v>
+      </c>
+      <c r="D306" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E306" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F306" s="3" t="s">
         <v>1635</v>
-      </c>
-      <c r="D306" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E306" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F306" s="3" t="s">
-        <v>1636</v>
       </c>
       <c r="G306" s="3">
         <v>27</v>
@@ -28073,13 +29400,13 @@
         <v>27</v>
       </c>
       <c r="J306" s="3" t="s">
+        <v>1636</v>
+      </c>
+      <c r="K306" s="3" t="s">
         <v>1637</v>
       </c>
-      <c r="K306" s="3" t="s">
+      <c r="L306" s="3" t="s">
         <v>1638</v>
-      </c>
-      <c r="L306" s="3" t="s">
-        <v>1639</v>
       </c>
       <c r="M306" s="3"/>
       <c r="N306" s="3">
@@ -28089,7 +29416,7 @@
         <v>28</v>
       </c>
       <c r="P306" s="3" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="307" spans="1:16" ht="12.75" customHeight="1">
@@ -28097,10 +29424,10 @@
         <v>310</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="C307" s="3" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="D307" s="3" t="s">
         <v>18</v>
@@ -28109,7 +29436,7 @@
         <v>19</v>
       </c>
       <c r="F307" s="3" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="G307" s="3">
         <v>44</v>
@@ -28121,13 +29448,13 @@
         <v>44</v>
       </c>
       <c r="J307" s="3" t="s">
+        <v>1641</v>
+      </c>
+      <c r="K307" s="3" t="s">
         <v>1642</v>
       </c>
-      <c r="K307" s="3" t="s">
+      <c r="L307" s="3" t="s">
         <v>1643</v>
-      </c>
-      <c r="L307" s="3" t="s">
-        <v>1644</v>
       </c>
       <c r="M307" s="3"/>
       <c r="N307" s="3">
@@ -28137,7 +29464,7 @@
         <v>45</v>
       </c>
       <c r="P307" s="3" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="308" spans="1:16" ht="12.75" customHeight="1">
@@ -28145,19 +29472,19 @@
         <v>311</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="C308" s="3" t="s">
+        <v>1645</v>
+      </c>
+      <c r="D308" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E308" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F308" s="3" t="s">
         <v>1646</v>
-      </c>
-      <c r="D308" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E308" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F308" s="3" t="s">
-        <v>1647</v>
       </c>
       <c r="G308" s="3">
         <v>111</v>
@@ -28169,13 +29496,13 @@
         <v>244</v>
       </c>
       <c r="J308" s="3" t="s">
+        <v>1647</v>
+      </c>
+      <c r="K308" s="3" t="s">
         <v>1648</v>
       </c>
-      <c r="K308" s="3" t="s">
+      <c r="L308" s="3" t="s">
         <v>1649</v>
-      </c>
-      <c r="L308" s="3" t="s">
-        <v>1650</v>
       </c>
       <c r="M308" s="3"/>
       <c r="N308" s="3">
@@ -28185,7 +29512,7 @@
         <v>113</v>
       </c>
       <c r="P308" s="3" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="309" spans="1:16" ht="12.75" customHeight="1">
@@ -28196,16 +29523,16 @@
         <v>326</v>
       </c>
       <c r="C309" s="3" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D309" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E309" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F309" s="3" t="s">
         <v>1651</v>
-      </c>
-      <c r="D309" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E309" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F309" s="3" t="s">
-        <v>1652</v>
       </c>
       <c r="G309" s="3">
         <v>139</v>
@@ -28217,13 +29544,13 @@
         <v>298</v>
       </c>
       <c r="J309" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="K309" s="3" t="s">
         <v>1653</v>
       </c>
-      <c r="K309" s="3" t="s">
+      <c r="L309" s="3" t="s">
         <v>1654</v>
-      </c>
-      <c r="L309" s="3" t="s">
-        <v>1655</v>
       </c>
       <c r="M309" s="3"/>
       <c r="N309" s="3">
@@ -28233,7 +29560,7 @@
         <v>141</v>
       </c>
       <c r="P309" s="3" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="310" spans="1:16" ht="12.75" customHeight="1">
@@ -28241,19 +29568,19 @@
         <v>313</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="C310" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="D310" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E310" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F310" s="3" t="s">
         <v>1656</v>
-      </c>
-      <c r="D310" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E310" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F310" s="3" t="s">
-        <v>1657</v>
       </c>
       <c r="G310" s="3">
         <v>2</v>
@@ -28265,13 +29592,13 @@
         <v>2</v>
       </c>
       <c r="J310" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="K310" s="3" t="s">
         <v>1658</v>
       </c>
-      <c r="K310" s="3" t="s">
+      <c r="L310" s="3" t="s">
         <v>1659</v>
-      </c>
-      <c r="L310" s="3" t="s">
-        <v>1660</v>
       </c>
       <c r="M310" s="3"/>
       <c r="N310" s="3">
@@ -28281,7 +29608,7 @@
         <v>1</v>
       </c>
       <c r="P310" s="3" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="311" spans="1:16" ht="12.75" customHeight="1">
@@ -28289,10 +29616,10 @@
         <v>314</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="C311" s="3" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="D311" s="3" t="s">
         <v>18</v>
@@ -28301,7 +29628,7 @@
         <v>19</v>
       </c>
       <c r="F311" s="3" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="G311" s="3">
         <v>3</v>
@@ -28313,13 +29640,13 @@
         <v>3</v>
       </c>
       <c r="J311" s="3" t="s">
+        <v>1661</v>
+      </c>
+      <c r="K311" s="3" t="s">
         <v>1662</v>
       </c>
-      <c r="K311" s="3" t="s">
+      <c r="L311" s="3" t="s">
         <v>1663</v>
-      </c>
-      <c r="L311" s="3" t="s">
-        <v>1664</v>
       </c>
       <c r="M311" s="3"/>
       <c r="N311" s="3">
@@ -28329,7 +29656,7 @@
         <v>116</v>
       </c>
       <c r="P311" s="3" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="312" spans="1:16" ht="12.75" customHeight="1">
@@ -28340,16 +29667,16 @@
         <v>31</v>
       </c>
       <c r="C312" s="3" t="s">
+        <v>1678</v>
+      </c>
+      <c r="D312" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E312" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F312" s="3" t="s">
         <v>1679</v>
-      </c>
-      <c r="D312" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E312" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F312" s="3" t="s">
-        <v>1680</v>
       </c>
       <c r="G312" s="3">
         <v>88</v>
@@ -28361,16 +29688,16 @@
         <v>88</v>
       </c>
       <c r="J312" s="3" t="s">
+        <v>1680</v>
+      </c>
+      <c r="K312" s="3" t="s">
         <v>1681</v>
       </c>
-      <c r="K312" s="3" t="s">
+      <c r="L312" s="3" t="s">
         <v>1682</v>
       </c>
-      <c r="L312" s="3" t="s">
+      <c r="M312" s="3" t="s">
         <v>1683</v>
-      </c>
-      <c r="M312" s="3" t="s">
-        <v>1684</v>
       </c>
       <c r="N312" s="3">
         <v>1</v>
@@ -28379,7 +29706,7 @@
         <v>235</v>
       </c>
       <c r="P312" s="3" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="313" spans="1:16" ht="12.75" customHeight="1">
@@ -28387,19 +29714,19 @@
         <v>316</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="C313" s="3" t="s">
+        <v>1686</v>
+      </c>
+      <c r="D313" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E313" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F313" s="3" t="s">
         <v>1687</v>
-      </c>
-      <c r="D313" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E313" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F313" s="3" t="s">
-        <v>1688</v>
       </c>
       <c r="G313" s="3">
         <v>43</v>
@@ -28408,16 +29735,16 @@
         <v>42</v>
       </c>
       <c r="I313" s="3" t="s">
+        <v>1688</v>
+      </c>
+      <c r="J313" s="3" t="s">
         <v>1689</v>
       </c>
-      <c r="J313" s="3" t="s">
+      <c r="K313" s="3" t="s">
         <v>1690</v>
       </c>
-      <c r="K313" s="3" t="s">
+      <c r="L313" s="3" t="s">
         <v>1691</v>
-      </c>
-      <c r="L313" s="3" t="s">
-        <v>1692</v>
       </c>
       <c r="M313" s="3"/>
       <c r="N313" s="3">
@@ -28427,7 +29754,7 @@
         <v>42</v>
       </c>
       <c r="P313" s="3" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="314" spans="1:16" ht="12.75" customHeight="1">
@@ -28438,16 +29765,16 @@
         <v>16</v>
       </c>
       <c r="C314" s="3" t="s">
+        <v>1693</v>
+      </c>
+      <c r="D314" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E314" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F314" s="3" t="s">
         <v>1694</v>
-      </c>
-      <c r="D314" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E314" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F314" s="3" t="s">
-        <v>1695</v>
       </c>
       <c r="G314" s="3">
         <v>72</v>
@@ -28459,13 +29786,13 @@
         <v>72</v>
       </c>
       <c r="J314" s="3" t="s">
+        <v>1695</v>
+      </c>
+      <c r="K314" s="3" t="s">
         <v>1696</v>
       </c>
-      <c r="K314" s="3" t="s">
+      <c r="L314" s="3" t="s">
         <v>1697</v>
-      </c>
-      <c r="L314" s="3" t="s">
-        <v>1698</v>
       </c>
       <c r="M314" s="3"/>
       <c r="N314" s="3">
@@ -28475,7 +29802,7 @@
         <v>189</v>
       </c>
       <c r="P314" s="3" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="315" spans="1:16" ht="12.75" customHeight="1">
@@ -28483,19 +29810,19 @@
         <v>318</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="C315" s="3" t="s">
+        <v>1698</v>
+      </c>
+      <c r="D315" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E315" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F315" s="3" t="s">
         <v>1699</v>
-      </c>
-      <c r="D315" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E315" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F315" s="3" t="s">
-        <v>1700</v>
       </c>
       <c r="G315" s="3">
         <v>41</v>
@@ -28507,13 +29834,13 @@
         <v>41</v>
       </c>
       <c r="J315" s="3" t="s">
+        <v>1700</v>
+      </c>
+      <c r="K315" s="3" t="s">
         <v>1701</v>
       </c>
-      <c r="K315" s="3" t="s">
+      <c r="L315" s="3" t="s">
         <v>1702</v>
-      </c>
-      <c r="L315" s="3" t="s">
-        <v>1703</v>
       </c>
       <c r="M315" s="3"/>
       <c r="N315" s="3">
@@ -28523,7 +29850,7 @@
         <v>266</v>
       </c>
       <c r="P315" s="3" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="316" spans="1:16" ht="12.75" customHeight="1">
@@ -28531,10 +29858,10 @@
         <v>319</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="C316" s="3" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="D316" s="3" t="s">
         <v>18</v>
@@ -28543,7 +29870,7 @@
         <v>19</v>
       </c>
       <c r="F316" s="3" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="G316" s="3">
         <v>88</v>
@@ -28555,13 +29882,13 @@
         <v>88</v>
       </c>
       <c r="J316" s="3" t="s">
+        <v>1705</v>
+      </c>
+      <c r="K316" s="3" t="s">
         <v>1706</v>
       </c>
-      <c r="K316" s="3" t="s">
+      <c r="L316" s="3" t="s">
         <v>1707</v>
-      </c>
-      <c r="L316" s="3" t="s">
-        <v>1708</v>
       </c>
       <c r="M316" s="3"/>
       <c r="N316" s="3">
@@ -28571,7 +29898,7 @@
         <v>89</v>
       </c>
       <c r="P316" s="3" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="317" spans="1:16" ht="12.75" customHeight="1">
@@ -28579,10 +29906,10 @@
         <v>320</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="C317" s="3" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="D317" s="3" t="s">
         <v>18</v>
@@ -28591,7 +29918,7 @@
         <v>19</v>
       </c>
       <c r="F317" s="3" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="G317" s="3">
         <v>97</v>
@@ -28603,13 +29930,13 @@
         <v>97</v>
       </c>
       <c r="J317" s="3" t="s">
+        <v>1709</v>
+      </c>
+      <c r="K317" s="3" t="s">
         <v>1710</v>
       </c>
-      <c r="K317" s="3" t="s">
+      <c r="L317" s="3" t="s">
         <v>1711</v>
-      </c>
-      <c r="L317" s="3" t="s">
-        <v>1712</v>
       </c>
       <c r="M317" s="3"/>
       <c r="N317" s="3">
@@ -28619,7 +29946,7 @@
         <v>315</v>
       </c>
       <c r="P317" s="3" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="318" spans="1:16" ht="12.75" customHeight="1">
@@ -28630,7 +29957,7 @@
         <v>31</v>
       </c>
       <c r="C318" s="3" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="D318" s="3" t="s">
         <v>18</v>
@@ -28639,7 +29966,7 @@
         <v>19</v>
       </c>
       <c r="F318" s="3" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="G318" s="3">
         <v>112</v>
@@ -28654,10 +29981,10 @@
         <v>1220</v>
       </c>
       <c r="K318" s="3" t="s">
+        <v>1714</v>
+      </c>
+      <c r="L318" s="3" t="s">
         <v>1715</v>
-      </c>
-      <c r="L318" s="3" t="s">
-        <v>1716</v>
       </c>
       <c r="M318" s="3"/>
       <c r="N318" s="3">
@@ -28667,7 +29994,7 @@
         <v>327</v>
       </c>
       <c r="P318" s="3" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="319" spans="1:16" ht="12.75" customHeight="1">
@@ -28678,7 +30005,7 @@
         <v>16</v>
       </c>
       <c r="C319" s="3" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="D319" s="3" t="s">
         <v>241</v>
@@ -28687,7 +30014,7 @@
         <v>19</v>
       </c>
       <c r="F319" s="3" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="G319" s="3">
         <v>155</v>
@@ -28699,13 +30026,13 @@
         <v>155</v>
       </c>
       <c r="J319" s="3" t="s">
+        <v>1718</v>
+      </c>
+      <c r="K319" s="3" t="s">
         <v>1719</v>
       </c>
-      <c r="K319" s="3" t="s">
+      <c r="L319" s="3" t="s">
         <v>1720</v>
-      </c>
-      <c r="L319" s="3" t="s">
-        <v>1721</v>
       </c>
       <c r="M319" s="3"/>
       <c r="N319" s="3">
@@ -28715,7 +30042,7 @@
         <v>371</v>
       </c>
       <c r="P319" s="3" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="320" spans="1:16" ht="12.75" customHeight="1">
@@ -28726,7 +30053,7 @@
         <v>16</v>
       </c>
       <c r="C320" s="3" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="D320" s="3" t="s">
         <v>18</v>
@@ -28735,7 +30062,7 @@
         <v>19</v>
       </c>
       <c r="F320" s="3" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="G320" s="3">
         <v>201</v>
@@ -28747,13 +30074,13 @@
         <v>201</v>
       </c>
       <c r="J320" s="3" t="s">
+        <v>1723</v>
+      </c>
+      <c r="K320" s="3" t="s">
         <v>1724</v>
       </c>
-      <c r="K320" s="3" t="s">
+      <c r="L320" s="3" t="s">
         <v>1725</v>
-      </c>
-      <c r="L320" s="3" t="s">
-        <v>1726</v>
       </c>
       <c r="M320" s="3"/>
       <c r="N320" s="3">
@@ -28763,7 +30090,7 @@
         <v>417</v>
       </c>
       <c r="P320" s="3" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="321" spans="1:16" ht="12.75" customHeight="1">
@@ -28774,16 +30101,16 @@
         <v>16</v>
       </c>
       <c r="C321" s="3" t="s">
+        <v>1726</v>
+      </c>
+      <c r="D321" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E321" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F321" s="3" t="s">
         <v>1727</v>
-      </c>
-      <c r="D321" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E321" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F321" s="3" t="s">
-        <v>1728</v>
       </c>
       <c r="G321" s="3">
         <v>93</v>
@@ -28795,13 +30122,13 @@
         <v>93</v>
       </c>
       <c r="J321" s="3" t="s">
+        <v>1728</v>
+      </c>
+      <c r="K321" s="3" t="s">
         <v>1729</v>
       </c>
-      <c r="K321" s="3" t="s">
-        <v>1730</v>
-      </c>
       <c r="L321" s="3" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="M321" s="3"/>
       <c r="N321" s="3">
@@ -28811,7 +30138,7 @@
         <v>94</v>
       </c>
       <c r="P321" s="3" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="322" spans="1:16" ht="12.75" customHeight="1">
@@ -28819,19 +30146,19 @@
         <v>325</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="C322" s="3" t="s">
+        <v>1730</v>
+      </c>
+      <c r="D322" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E322" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F322" s="3" t="s">
         <v>1731</v>
-      </c>
-      <c r="D322" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E322" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F322" s="3" t="s">
-        <v>1732</v>
       </c>
       <c r="G322" s="3">
         <v>117</v>
@@ -28846,10 +30173,10 @@
         <v>274</v>
       </c>
       <c r="K322" s="3" t="s">
+        <v>1732</v>
+      </c>
+      <c r="L322" s="3" t="s">
         <v>1733</v>
-      </c>
-      <c r="L322" s="3" t="s">
-        <v>1734</v>
       </c>
       <c r="M322" s="3"/>
       <c r="N322" s="3">
@@ -28859,7 +30186,7 @@
         <v>118</v>
       </c>
       <c r="P322" s="3" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="323" spans="1:16" ht="12.75" customHeight="1">
@@ -28867,10 +30194,10 @@
         <v>326</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="C323" s="3" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="D323" s="3" t="s">
         <v>18</v>
@@ -28879,7 +30206,7 @@
         <v>19</v>
       </c>
       <c r="F323" s="3" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="G323" s="3">
         <v>120</v>
@@ -28891,13 +30218,13 @@
         <v>120</v>
       </c>
       <c r="J323" s="3" t="s">
+        <v>1736</v>
+      </c>
+      <c r="K323" s="3" t="s">
         <v>1737</v>
       </c>
-      <c r="K323" s="3" t="s">
+      <c r="L323" s="3" t="s">
         <v>1738</v>
-      </c>
-      <c r="L323" s="3" t="s">
-        <v>1739</v>
       </c>
       <c r="M323" s="3"/>
       <c r="N323" s="3">
@@ -28907,7 +30234,7 @@
         <v>121</v>
       </c>
       <c r="P323" s="3" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="324" spans="1:16" ht="12.75" customHeight="1">
@@ -28918,7 +30245,7 @@
         <v>585</v>
       </c>
       <c r="C324" s="3" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="D324" s="3" t="s">
         <v>241</v>
@@ -28927,7 +30254,7 @@
         <v>19</v>
       </c>
       <c r="F324" s="3" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="G324" s="3">
         <v>159</v>
@@ -28936,16 +30263,16 @@
         <v>160</v>
       </c>
       <c r="I324" s="3" t="s">
+        <v>1741</v>
+      </c>
+      <c r="J324" s="3" t="s">
         <v>1742</v>
       </c>
-      <c r="J324" s="3" t="s">
+      <c r="K324" s="3" t="s">
         <v>1743</v>
       </c>
-      <c r="K324" s="3" t="s">
+      <c r="L324" s="3" t="s">
         <v>1744</v>
-      </c>
-      <c r="L324" s="3" t="s">
-        <v>1745</v>
       </c>
       <c r="M324" s="3"/>
       <c r="N324" s="3">
@@ -28955,7 +30282,7 @@
         <v>160</v>
       </c>
       <c r="P324" s="3" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="325" spans="1:16" ht="12.75" customHeight="1">
@@ -28963,19 +30290,19 @@
         <v>328</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="C325" s="3" t="s">
+        <v>1745</v>
+      </c>
+      <c r="D325" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E325" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F325" s="3" t="s">
         <v>1746</v>
-      </c>
-      <c r="D325" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E325" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F325" s="3" t="s">
-        <v>1747</v>
       </c>
       <c r="G325" s="3">
         <v>172</v>
@@ -28987,13 +30314,13 @@
         <v>357</v>
       </c>
       <c r="J325" s="3" t="s">
+        <v>1747</v>
+      </c>
+      <c r="K325" s="3" t="s">
         <v>1748</v>
       </c>
-      <c r="K325" s="3" t="s">
+      <c r="L325" s="3" t="s">
         <v>1749</v>
-      </c>
-      <c r="L325" s="3" t="s">
-        <v>1750</v>
       </c>
       <c r="M325" s="3"/>
       <c r="N325" s="3">
@@ -29003,7 +30330,7 @@
         <v>361</v>
       </c>
       <c r="P325" s="3" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="326" spans="1:16" ht="12.75" customHeight="1">
@@ -29011,19 +30338,19 @@
         <v>329</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="C326" s="3" t="s">
+        <v>1750</v>
+      </c>
+      <c r="D326" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E326" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F326" s="3" t="s">
         <v>1751</v>
-      </c>
-      <c r="D326" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E326" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F326" s="3" t="s">
-        <v>1752</v>
       </c>
       <c r="G326" s="3">
         <v>24</v>
@@ -29035,13 +30362,13 @@
         <v>24</v>
       </c>
       <c r="J326" s="3" t="s">
+        <v>1752</v>
+      </c>
+      <c r="K326" s="3" t="s">
         <v>1753</v>
       </c>
-      <c r="K326" s="3" t="s">
+      <c r="L326" s="3" t="s">
         <v>1754</v>
-      </c>
-      <c r="L326" s="3" t="s">
-        <v>1755</v>
       </c>
       <c r="M326" s="3"/>
       <c r="N326" s="3">
@@ -29051,7 +30378,7 @@
         <v>25</v>
       </c>
       <c r="P326" s="3" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="327" spans="1:16" ht="12.75" customHeight="1">
@@ -29059,10 +30386,10 @@
         <v>330</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="C327" s="3" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="D327" s="3" t="s">
         <v>18</v>
@@ -29071,7 +30398,7 @@
         <v>19</v>
       </c>
       <c r="F327" s="3" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="G327" s="3">
         <v>51</v>
@@ -29083,13 +30410,13 @@
         <v>51</v>
       </c>
       <c r="J327" s="3" t="s">
+        <v>1757</v>
+      </c>
+      <c r="K327" s="3" t="s">
         <v>1758</v>
       </c>
-      <c r="K327" s="3" t="s">
+      <c r="L327" s="3" t="s">
         <v>1759</v>
-      </c>
-      <c r="L327" s="3" t="s">
-        <v>1760</v>
       </c>
       <c r="M327" s="3"/>
       <c r="N327" s="3">
@@ -29099,7 +30426,7 @@
         <v>176</v>
       </c>
       <c r="P327" s="3" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="328" spans="1:16" ht="12.75" customHeight="1">
@@ -29107,10 +30434,10 @@
         <v>331</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="C328" s="3" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="D328" s="3" t="s">
         <v>18</v>
@@ -29119,7 +30446,7 @@
         <v>19</v>
       </c>
       <c r="F328" s="3" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="G328" s="3">
         <v>55</v>
@@ -29131,13 +30458,13 @@
         <v>55</v>
       </c>
       <c r="J328" s="3" t="s">
+        <v>1762</v>
+      </c>
+      <c r="K328" s="3" t="s">
         <v>1763</v>
       </c>
-      <c r="K328" s="3" t="s">
+      <c r="L328" s="3" t="s">
         <v>1764</v>
-      </c>
-      <c r="L328" s="3" t="s">
-        <v>1765</v>
       </c>
       <c r="M328" s="3"/>
       <c r="N328" s="3">
@@ -29147,7 +30474,7 @@
         <v>179</v>
       </c>
       <c r="P328" s="3" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="329" spans="1:16" ht="12.75" customHeight="1">
@@ -29155,10 +30482,10 @@
         <v>332</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="C329" s="3" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="D329" s="3" t="s">
         <v>18</v>
@@ -29167,7 +30494,7 @@
         <v>19</v>
       </c>
       <c r="F329" s="3" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="G329" s="3">
         <v>10</v>
@@ -29179,13 +30506,13 @@
         <v>137</v>
       </c>
       <c r="J329" s="3" t="s">
+        <v>1766</v>
+      </c>
+      <c r="K329" s="3" t="s">
         <v>1767</v>
       </c>
-      <c r="K329" s="3" t="s">
+      <c r="L329" s="3" t="s">
         <v>1768</v>
-      </c>
-      <c r="L329" s="3" t="s">
-        <v>1769</v>
       </c>
       <c r="M329" s="3"/>
       <c r="N329" s="3">
@@ -29195,7 +30522,7 @@
         <v>135</v>
       </c>
       <c r="P329" s="3" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="330" spans="1:16" ht="12.75" customHeight="1">
@@ -29203,10 +30530,10 @@
         <v>333</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="C330" s="3" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="D330" s="3" t="s">
         <v>18</v>
@@ -29215,7 +30542,7 @@
         <v>19</v>
       </c>
       <c r="F330" s="3" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="G330" s="3">
         <v>13</v>
@@ -29227,13 +30554,13 @@
         <v>139</v>
       </c>
       <c r="J330" s="3" t="s">
+        <v>1770</v>
+      </c>
+      <c r="K330" s="3" t="s">
         <v>1771</v>
       </c>
-      <c r="K330" s="3" t="s">
+      <c r="L330" s="3" t="s">
         <v>1772</v>
-      </c>
-      <c r="L330" s="3" t="s">
-        <v>1773</v>
       </c>
       <c r="M330" s="3"/>
       <c r="N330" s="3">
@@ -29243,7 +30570,7 @@
         <v>11</v>
       </c>
       <c r="P330" s="3" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="331" spans="1:16" ht="12.75" customHeight="1">
@@ -29251,10 +30578,10 @@
         <v>334</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="C331" s="3" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="D331" s="3" t="s">
         <v>18</v>
@@ -29263,7 +30590,7 @@
         <v>19</v>
       </c>
       <c r="F331" s="3" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="G331" s="3">
         <v>81</v>
@@ -29275,13 +30602,13 @@
         <v>198</v>
       </c>
       <c r="J331" s="3" t="s">
+        <v>1774</v>
+      </c>
+      <c r="K331" s="3" t="s">
         <v>1775</v>
       </c>
-      <c r="K331" s="3" t="s">
+      <c r="L331" s="3" t="s">
         <v>1776</v>
-      </c>
-      <c r="L331" s="3" t="s">
-        <v>1777</v>
       </c>
       <c r="M331" s="3"/>
       <c r="N331" s="3">
@@ -29291,7 +30618,7 @@
         <v>79</v>
       </c>
       <c r="P331" s="3" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="332" spans="1:16" ht="12.75" customHeight="1">
@@ -29299,19 +30626,19 @@
         <v>335</v>
       </c>
       <c r="B332" s="3" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="C332" s="3" t="s">
+        <v>1777</v>
+      </c>
+      <c r="D332" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E332" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F332" s="3" t="s">
         <v>1778</v>
-      </c>
-      <c r="D332" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E332" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F332" s="3" t="s">
-        <v>1779</v>
       </c>
       <c r="G332" s="3">
         <v>12</v>
@@ -29323,13 +30650,13 @@
         <v>12</v>
       </c>
       <c r="J332" s="3" t="s">
+        <v>1779</v>
+      </c>
+      <c r="K332" s="3" t="s">
         <v>1780</v>
       </c>
-      <c r="K332" s="3" t="s">
+      <c r="L332" s="3" t="s">
         <v>1781</v>
-      </c>
-      <c r="L332" s="3" t="s">
-        <v>1782</v>
       </c>
       <c r="M332" s="3"/>
       <c r="N332" s="3">
@@ -29339,7 +30666,7 @@
         <v>126</v>
       </c>
       <c r="P332" s="3" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="333" spans="1:16" ht="12.75" customHeight="1">
@@ -29347,10 +30674,10 @@
         <v>336</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="C333" s="3" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="D333" s="3" t="s">
         <v>18</v>
@@ -29359,7 +30686,7 @@
         <v>19</v>
       </c>
       <c r="F333" s="3" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="G333" s="3">
         <v>120</v>
@@ -29371,13 +30698,13 @@
         <v>210</v>
       </c>
       <c r="J333" s="3" t="s">
+        <v>1783</v>
+      </c>
+      <c r="K333" s="3" t="s">
         <v>1784</v>
       </c>
-      <c r="K333" s="3" t="s">
+      <c r="L333" s="3" t="s">
         <v>1785</v>
-      </c>
-      <c r="L333" s="3" t="s">
-        <v>1786</v>
       </c>
       <c r="M333" s="3"/>
       <c r="N333" s="3">
@@ -29387,7 +30714,7 @@
         <v>227</v>
       </c>
       <c r="P333" s="3" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="334" spans="1:16" ht="12.75" customHeight="1">
@@ -29395,19 +30722,19 @@
         <v>337</v>
       </c>
       <c r="B334" s="3" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="C334" s="3" t="s">
+        <v>1786</v>
+      </c>
+      <c r="D334" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E334" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F334" s="3" t="s">
         <v>1787</v>
-      </c>
-      <c r="D334" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E334" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F334" s="3" t="s">
-        <v>1788</v>
       </c>
       <c r="G334" s="3">
         <v>52</v>
@@ -29419,13 +30746,13 @@
         <v>52</v>
       </c>
       <c r="J334" s="3" t="s">
+        <v>1788</v>
+      </c>
+      <c r="K334" s="3" t="s">
         <v>1789</v>
       </c>
-      <c r="K334" s="3" t="s">
+      <c r="L334" s="3" t="s">
         <v>1790</v>
-      </c>
-      <c r="L334" s="3" t="s">
-        <v>1791</v>
       </c>
       <c r="M334" s="3"/>
       <c r="N334" s="3">
@@ -29435,7 +30762,7 @@
         <v>53</v>
       </c>
       <c r="P334" s="3" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="335" spans="1:16" ht="12.75" customHeight="1">
@@ -29446,16 +30773,16 @@
         <v>16</v>
       </c>
       <c r="C335" s="3" t="s">
+        <v>1791</v>
+      </c>
+      <c r="D335" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E335" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F335" s="3" t="s">
         <v>1792</v>
-      </c>
-      <c r="D335" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E335" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F335" s="3" t="s">
-        <v>1793</v>
       </c>
       <c r="G335" s="3">
         <v>40</v>
@@ -29467,13 +30794,13 @@
         <v>228</v>
       </c>
       <c r="J335" s="3" t="s">
+        <v>1793</v>
+      </c>
+      <c r="K335" s="3" t="s">
         <v>1794</v>
       </c>
-      <c r="K335" s="3" t="s">
+      <c r="L335" s="3" t="s">
         <v>1795</v>
-      </c>
-      <c r="L335" s="3" t="s">
-        <v>1796</v>
       </c>
       <c r="M335" s="3"/>
       <c r="N335" s="3">
@@ -29483,7 +30810,7 @@
         <v>229</v>
       </c>
       <c r="P335" s="3" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="336" spans="1:16" ht="12.75" customHeight="1">
@@ -29491,19 +30818,19 @@
         <v>339</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="C336" s="3" t="s">
+        <v>1796</v>
+      </c>
+      <c r="D336" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E336" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F336" s="3" t="s">
         <v>1797</v>
-      </c>
-      <c r="D336" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E336" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F336" s="3" t="s">
-        <v>1798</v>
       </c>
       <c r="G336" s="3">
         <v>92</v>
@@ -29515,13 +30842,13 @@
         <v>149</v>
       </c>
       <c r="J336" s="3" t="s">
+        <v>1798</v>
+      </c>
+      <c r="K336" s="3" t="s">
         <v>1799</v>
       </c>
-      <c r="K336" s="3" t="s">
-        <v>1800</v>
-      </c>
       <c r="L336" s="3" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="M336" s="3"/>
       <c r="N336" s="3">
@@ -29531,7 +30858,1639 @@
         <v>161</v>
       </c>
       <c r="P336" s="3" t="s">
-        <v>1799</v>
+        <v>1798</v>
+      </c>
+    </row>
+    <row r="337" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A337" s="3">
+        <v>340</v>
+      </c>
+      <c r="B337" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C337" s="3" t="s">
+        <v>1815</v>
+      </c>
+      <c r="D337" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E337" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F337" s="3" t="s">
+        <v>1816</v>
+      </c>
+      <c r="G337" s="3">
+        <v>71</v>
+      </c>
+      <c r="H337" s="3">
+        <v>72</v>
+      </c>
+      <c r="I337" s="3">
+        <v>71</v>
+      </c>
+      <c r="J337" s="3" t="s">
+        <v>1817</v>
+      </c>
+      <c r="K337" s="3" t="s">
+        <v>1818</v>
+      </c>
+      <c r="L337" s="3" t="s">
+        <v>1819</v>
+      </c>
+      <c r="M337" s="3"/>
+      <c r="N337" s="3">
+        <v>1</v>
+      </c>
+      <c r="O337" s="3">
+        <v>72</v>
+      </c>
+      <c r="P337" s="3" t="s">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="338" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A338" s="3">
+        <v>341</v>
+      </c>
+      <c r="B338" s="3" t="s">
+        <v>1981</v>
+      </c>
+      <c r="C338" s="3" t="s">
+        <v>1821</v>
+      </c>
+      <c r="D338" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E338" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F338" s="3" t="s">
+        <v>1822</v>
+      </c>
+      <c r="G338" s="3">
+        <v>118</v>
+      </c>
+      <c r="H338" s="3">
+        <v>119</v>
+      </c>
+      <c r="I338" s="3">
+        <v>118</v>
+      </c>
+      <c r="J338" s="3" t="s">
+        <v>1823</v>
+      </c>
+      <c r="K338" s="3" t="s">
+        <v>1824</v>
+      </c>
+      <c r="L338" s="3" t="s">
+        <v>1825</v>
+      </c>
+      <c r="M338" s="3"/>
+      <c r="N338" s="3">
+        <v>1</v>
+      </c>
+      <c r="O338" s="3">
+        <v>119</v>
+      </c>
+      <c r="P338" s="3" t="s">
+        <v>1826</v>
+      </c>
+    </row>
+    <row r="339" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A339" s="3">
+        <v>342</v>
+      </c>
+      <c r="B339" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="C339" s="3" t="s">
+        <v>1827</v>
+      </c>
+      <c r="D339" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="E339" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F339" s="3" t="s">
+        <v>1822</v>
+      </c>
+      <c r="G339" s="3">
+        <v>123</v>
+      </c>
+      <c r="H339" s="3">
+        <v>124</v>
+      </c>
+      <c r="I339" s="3">
+        <v>123</v>
+      </c>
+      <c r="J339" s="3" t="s">
+        <v>1828</v>
+      </c>
+      <c r="K339" s="3" t="s">
+        <v>1829</v>
+      </c>
+      <c r="L339" s="3" t="s">
+        <v>1830</v>
+      </c>
+      <c r="M339" s="3"/>
+      <c r="N339" s="3">
+        <v>1</v>
+      </c>
+      <c r="O339" s="3">
+        <v>124</v>
+      </c>
+      <c r="P339" s="3" t="s">
+        <v>1828</v>
+      </c>
+    </row>
+    <row r="340" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A340" s="3">
+        <v>343</v>
+      </c>
+      <c r="B340" s="3" t="s">
+        <v>1982</v>
+      </c>
+      <c r="C340" s="3" t="s">
+        <v>1831</v>
+      </c>
+      <c r="D340" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E340" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F340" s="3" t="s">
+        <v>1832</v>
+      </c>
+      <c r="G340" s="3">
+        <v>97</v>
+      </c>
+      <c r="H340" s="3">
+        <v>98</v>
+      </c>
+      <c r="I340" s="3">
+        <v>97</v>
+      </c>
+      <c r="J340" s="3" t="s">
+        <v>1833</v>
+      </c>
+      <c r="K340" s="3" t="s">
+        <v>1834</v>
+      </c>
+      <c r="L340" s="3" t="s">
+        <v>1835</v>
+      </c>
+      <c r="M340" s="3"/>
+      <c r="N340" s="3">
+        <v>1</v>
+      </c>
+      <c r="O340" s="3">
+        <v>98</v>
+      </c>
+      <c r="P340" s="3" t="s">
+        <v>1836</v>
+      </c>
+    </row>
+    <row r="341" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A341" s="3">
+        <v>344</v>
+      </c>
+      <c r="B341" s="3" t="s">
+        <v>1983</v>
+      </c>
+      <c r="C341" s="3" t="s">
+        <v>1837</v>
+      </c>
+      <c r="D341" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E341" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F341" s="3" t="s">
+        <v>1832</v>
+      </c>
+      <c r="G341" s="3">
+        <v>144</v>
+      </c>
+      <c r="H341" s="3">
+        <v>143</v>
+      </c>
+      <c r="I341" s="3">
+        <v>144</v>
+      </c>
+      <c r="J341" s="3" t="s">
+        <v>1838</v>
+      </c>
+      <c r="K341" s="3" t="s">
+        <v>1839</v>
+      </c>
+      <c r="L341" s="3" t="s">
+        <v>1840</v>
+      </c>
+      <c r="M341" s="3"/>
+      <c r="N341" s="3">
+        <v>1</v>
+      </c>
+      <c r="O341" s="3">
+        <v>143</v>
+      </c>
+      <c r="P341" s="3" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="342" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A342" s="3">
+        <v>345</v>
+      </c>
+      <c r="B342" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C342" s="3" t="s">
+        <v>1842</v>
+      </c>
+      <c r="D342" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E342" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F342" s="3" t="s">
+        <v>1843</v>
+      </c>
+      <c r="G342" s="3">
+        <v>73</v>
+      </c>
+      <c r="H342" s="3">
+        <v>74</v>
+      </c>
+      <c r="I342" s="3">
+        <v>73</v>
+      </c>
+      <c r="J342" s="3" t="s">
+        <v>1844</v>
+      </c>
+      <c r="K342" s="3" t="s">
+        <v>1845</v>
+      </c>
+      <c r="L342" s="3" t="s">
+        <v>1846</v>
+      </c>
+      <c r="M342" s="3"/>
+      <c r="N342" s="3">
+        <v>1</v>
+      </c>
+      <c r="O342" s="3">
+        <v>198</v>
+      </c>
+      <c r="P342" s="3" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="343" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A343" s="3">
+        <v>346</v>
+      </c>
+      <c r="B343" s="22" t="s">
+        <v>1984</v>
+      </c>
+      <c r="C343" s="3" t="s">
+        <v>1847</v>
+      </c>
+      <c r="D343" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E343" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F343" s="3" t="s">
+        <v>1843</v>
+      </c>
+      <c r="G343" s="3">
+        <v>127</v>
+      </c>
+      <c r="H343" s="3">
+        <v>54</v>
+      </c>
+      <c r="I343" s="3">
+        <v>251</v>
+      </c>
+      <c r="J343" s="3" t="s">
+        <v>1848</v>
+      </c>
+      <c r="K343" s="3" t="s">
+        <v>1849</v>
+      </c>
+      <c r="L343" s="3" t="s">
+        <v>1850</v>
+      </c>
+      <c r="M343" s="3"/>
+      <c r="N343" s="3">
+        <v>1</v>
+      </c>
+      <c r="O343" s="3">
+        <v>257</v>
+      </c>
+      <c r="P343" s="3" t="s">
+        <v>1851</v>
+      </c>
+    </row>
+    <row r="344" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A344" s="3">
+        <v>347</v>
+      </c>
+      <c r="B344" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C344" s="3" t="s">
+        <v>1852</v>
+      </c>
+      <c r="D344" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E344" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F344" s="3" t="s">
+        <v>1853</v>
+      </c>
+      <c r="G344" s="3">
+        <v>30</v>
+      </c>
+      <c r="H344" s="3">
+        <v>31</v>
+      </c>
+      <c r="I344" s="3">
+        <v>30</v>
+      </c>
+      <c r="J344" s="3" t="s">
+        <v>1854</v>
+      </c>
+      <c r="K344" s="3" t="s">
+        <v>1855</v>
+      </c>
+      <c r="L344" s="3" t="s">
+        <v>1856</v>
+      </c>
+      <c r="M344" s="3"/>
+      <c r="N344" s="3">
+        <v>1</v>
+      </c>
+      <c r="O344" s="3">
+        <v>31</v>
+      </c>
+      <c r="P344" s="3" t="s">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="345" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A345" s="3">
+        <v>348</v>
+      </c>
+      <c r="B345" s="22" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C345" s="3" t="s">
+        <v>1858</v>
+      </c>
+      <c r="D345" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E345" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F345" s="3" t="s">
+        <v>1853</v>
+      </c>
+      <c r="G345" s="3">
+        <v>120</v>
+      </c>
+      <c r="H345" s="3">
+        <v>8</v>
+      </c>
+      <c r="I345" s="3">
+        <v>142</v>
+      </c>
+      <c r="J345" s="3" t="s">
+        <v>1859</v>
+      </c>
+      <c r="K345" s="3" t="s">
+        <v>1860</v>
+      </c>
+      <c r="L345" s="3" t="s">
+        <v>1861</v>
+      </c>
+      <c r="M345" s="3"/>
+      <c r="N345" s="3">
+        <v>1</v>
+      </c>
+      <c r="O345" s="3">
+        <v>180</v>
+      </c>
+      <c r="P345" s="3" t="s">
+        <v>1859</v>
+      </c>
+    </row>
+    <row r="346" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A346" s="3">
+        <v>349</v>
+      </c>
+      <c r="B346" s="3" t="s">
+        <v>1986</v>
+      </c>
+      <c r="C346" s="3" t="s">
+        <v>1862</v>
+      </c>
+      <c r="D346" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E346" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F346" s="3" t="s">
+        <v>1863</v>
+      </c>
+      <c r="G346" s="3">
+        <v>30</v>
+      </c>
+      <c r="H346" s="3">
+        <v>31</v>
+      </c>
+      <c r="I346" s="3">
+        <v>30</v>
+      </c>
+      <c r="J346" s="3" t="s">
+        <v>1864</v>
+      </c>
+      <c r="K346" s="3" t="s">
+        <v>1865</v>
+      </c>
+      <c r="L346" s="3" t="s">
+        <v>1866</v>
+      </c>
+      <c r="M346" s="3"/>
+      <c r="N346" s="3">
+        <v>1</v>
+      </c>
+      <c r="O346" s="3">
+        <v>162</v>
+      </c>
+      <c r="P346" s="3" t="s">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="347" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A347" s="3">
+        <v>350</v>
+      </c>
+      <c r="B347" s="3" t="s">
+        <v>1871</v>
+      </c>
+      <c r="C347" s="3" t="s">
+        <v>1867</v>
+      </c>
+      <c r="D347" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E347" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F347" s="3" t="s">
+        <v>1868</v>
+      </c>
+      <c r="G347" s="3">
+        <v>46</v>
+      </c>
+      <c r="H347" s="3">
+        <v>25</v>
+      </c>
+      <c r="I347" s="3">
+        <v>186</v>
+      </c>
+      <c r="J347" s="3" t="s">
+        <v>1869</v>
+      </c>
+      <c r="K347" s="3" t="s">
+        <v>1870</v>
+      </c>
+      <c r="L347" s="3" t="s">
+        <v>1871</v>
+      </c>
+      <c r="M347" s="3"/>
+      <c r="N347" s="3">
+        <v>1</v>
+      </c>
+      <c r="O347" s="3">
+        <v>183</v>
+      </c>
+      <c r="P347" s="3" t="s">
+        <v>1872</v>
+      </c>
+    </row>
+    <row r="348" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A348" s="3">
+        <v>351</v>
+      </c>
+      <c r="B348" s="3" t="s">
+        <v>1987</v>
+      </c>
+      <c r="C348" s="3" t="s">
+        <v>1873</v>
+      </c>
+      <c r="D348" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E348" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F348" s="3" t="s">
+        <v>1868</v>
+      </c>
+      <c r="G348" s="3">
+        <v>70</v>
+      </c>
+      <c r="H348" s="3">
+        <v>67</v>
+      </c>
+      <c r="I348" s="3">
+        <v>200</v>
+      </c>
+      <c r="J348" s="3" t="s">
+        <v>1461</v>
+      </c>
+      <c r="K348" s="3" t="s">
+        <v>1874</v>
+      </c>
+      <c r="L348" s="3" t="s">
+        <v>1875</v>
+      </c>
+      <c r="M348" s="3"/>
+      <c r="N348" s="3">
+        <v>1</v>
+      </c>
+      <c r="O348" s="3">
+        <v>207</v>
+      </c>
+      <c r="P348" s="3" t="s">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="349" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A349" s="3">
+        <v>352</v>
+      </c>
+      <c r="B349" s="3" t="s">
+        <v>1988</v>
+      </c>
+      <c r="C349" s="3" t="s">
+        <v>1876</v>
+      </c>
+      <c r="D349" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E349" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F349" s="3" t="s">
+        <v>1868</v>
+      </c>
+      <c r="G349" s="3">
+        <v>48</v>
+      </c>
+      <c r="H349" s="3">
+        <v>67</v>
+      </c>
+      <c r="I349" s="3">
+        <v>216</v>
+      </c>
+      <c r="J349" s="3" t="s">
+        <v>1877</v>
+      </c>
+      <c r="K349" s="3" t="s">
+        <v>1878</v>
+      </c>
+      <c r="L349" s="3" t="s">
+        <v>1879</v>
+      </c>
+      <c r="M349" s="3"/>
+      <c r="N349" s="3">
+        <v>1</v>
+      </c>
+      <c r="O349" s="3">
+        <v>210</v>
+      </c>
+      <c r="P349" s="3" t="s">
+        <v>1877</v>
+      </c>
+    </row>
+    <row r="350" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A350" s="3">
+        <v>353</v>
+      </c>
+      <c r="B350" s="3" t="s">
+        <v>1871</v>
+      </c>
+      <c r="C350" s="3" t="s">
+        <v>1880</v>
+      </c>
+      <c r="D350" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E350" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F350" s="3" t="s">
+        <v>1868</v>
+      </c>
+      <c r="G350" s="3">
+        <v>74</v>
+      </c>
+      <c r="H350" s="3">
+        <v>90</v>
+      </c>
+      <c r="I350" s="3">
+        <v>217</v>
+      </c>
+      <c r="J350" s="3" t="s">
+        <v>1881</v>
+      </c>
+      <c r="K350" s="3" t="s">
+        <v>1882</v>
+      </c>
+      <c r="L350" s="3" t="s">
+        <v>1871</v>
+      </c>
+      <c r="M350" s="3"/>
+      <c r="N350" s="3">
+        <v>1</v>
+      </c>
+      <c r="O350" s="3">
+        <v>251</v>
+      </c>
+      <c r="P350" s="3" t="s">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="351" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A351" s="3">
+        <v>354</v>
+      </c>
+      <c r="B351" s="3" t="s">
+        <v>1871</v>
+      </c>
+      <c r="C351" s="3" t="s">
+        <v>1883</v>
+      </c>
+      <c r="D351" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E351" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F351" s="3" t="s">
+        <v>1868</v>
+      </c>
+      <c r="G351" s="3">
+        <v>111</v>
+      </c>
+      <c r="H351" s="3">
+        <v>90</v>
+      </c>
+      <c r="I351" s="3">
+        <v>242</v>
+      </c>
+      <c r="J351" s="3" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K351" s="3" t="s">
+        <v>1885</v>
+      </c>
+      <c r="L351" s="3" t="s">
+        <v>1871</v>
+      </c>
+      <c r="M351" s="3"/>
+      <c r="N351" s="3">
+        <v>1</v>
+      </c>
+      <c r="O351" s="3">
+        <v>248</v>
+      </c>
+      <c r="P351" s="3" t="s">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="352" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A352" s="3">
+        <v>355</v>
+      </c>
+      <c r="B352" s="3" t="s">
+        <v>1988</v>
+      </c>
+      <c r="C352" s="3" t="s">
+        <v>1887</v>
+      </c>
+      <c r="D352" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E352" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F352" s="3" t="s">
+        <v>1868</v>
+      </c>
+      <c r="G352" s="3">
+        <v>116</v>
+      </c>
+      <c r="H352" s="3">
+        <v>128</v>
+      </c>
+      <c r="I352" s="3">
+        <v>257</v>
+      </c>
+      <c r="J352" s="3" t="s">
+        <v>1888</v>
+      </c>
+      <c r="K352" s="3" t="s">
+        <v>1889</v>
+      </c>
+      <c r="L352" s="3" t="s">
+        <v>1890</v>
+      </c>
+      <c r="M352" s="3"/>
+      <c r="N352" s="3">
+        <v>1</v>
+      </c>
+      <c r="O352" s="3">
+        <v>279</v>
+      </c>
+      <c r="P352" s="3" t="s">
+        <v>1888</v>
+      </c>
+    </row>
+    <row r="353" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A353" s="3">
+        <v>356</v>
+      </c>
+      <c r="B353" s="3" t="s">
+        <v>1894</v>
+      </c>
+      <c r="C353" s="3" t="s">
+        <v>1891</v>
+      </c>
+      <c r="D353" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E353" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F353" s="3" t="s">
+        <v>1868</v>
+      </c>
+      <c r="G353" s="3">
+        <v>143</v>
+      </c>
+      <c r="H353" s="3">
+        <v>128</v>
+      </c>
+      <c r="I353" s="3">
+        <v>271</v>
+      </c>
+      <c r="J353" s="3" t="s">
+        <v>1892</v>
+      </c>
+      <c r="K353" s="3" t="s">
+        <v>1893</v>
+      </c>
+      <c r="L353" s="3" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M353" s="3"/>
+      <c r="N353" s="3">
+        <v>1</v>
+      </c>
+      <c r="O353" s="3">
+        <v>275</v>
+      </c>
+      <c r="P353" s="3" t="s">
+        <v>1892</v>
+      </c>
+    </row>
+    <row r="354" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A354" s="3">
+        <v>357</v>
+      </c>
+      <c r="B354" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C354" s="3" t="s">
+        <v>1895</v>
+      </c>
+      <c r="D354" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E354" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F354" s="3" t="s">
+        <v>1868</v>
+      </c>
+      <c r="G354" s="3">
+        <v>40</v>
+      </c>
+      <c r="H354" s="3">
+        <v>41</v>
+      </c>
+      <c r="I354" s="3" t="s">
+        <v>1896</v>
+      </c>
+      <c r="J354" s="3" t="s">
+        <v>1897</v>
+      </c>
+      <c r="K354" s="3" t="s">
+        <v>1898</v>
+      </c>
+      <c r="L354" s="3" t="s">
+        <v>1899</v>
+      </c>
+      <c r="M354" s="3"/>
+      <c r="N354" s="3">
+        <v>1</v>
+      </c>
+      <c r="O354" s="3">
+        <v>41</v>
+      </c>
+      <c r="P354" s="3" t="s">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="355" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A355" s="3">
+        <v>358</v>
+      </c>
+      <c r="B355" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C355" s="3" t="s">
+        <v>1900</v>
+      </c>
+      <c r="D355" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E355" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F355" s="3" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G355" s="3">
+        <v>56</v>
+      </c>
+      <c r="H355" s="3">
+        <v>57</v>
+      </c>
+      <c r="I355" s="3">
+        <v>56</v>
+      </c>
+      <c r="J355" s="3" t="s">
+        <v>1902</v>
+      </c>
+      <c r="K355" s="3" t="s">
+        <v>1903</v>
+      </c>
+      <c r="L355" s="3" t="s">
+        <v>1904</v>
+      </c>
+      <c r="M355" s="3"/>
+      <c r="N355" s="3">
+        <v>1</v>
+      </c>
+      <c r="O355" s="3">
+        <v>57</v>
+      </c>
+      <c r="P355" s="3" t="s">
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="356" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A356" s="3">
+        <v>359</v>
+      </c>
+      <c r="B356" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C356" s="3" t="s">
+        <v>1906</v>
+      </c>
+      <c r="D356" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E356" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F356" s="3" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G356" s="3">
+        <v>74</v>
+      </c>
+      <c r="H356" s="3">
+        <v>75</v>
+      </c>
+      <c r="I356" s="3">
+        <v>74</v>
+      </c>
+      <c r="J356" s="3" t="s">
+        <v>1907</v>
+      </c>
+      <c r="K356" s="3" t="s">
+        <v>1908</v>
+      </c>
+      <c r="L356" s="3" t="s">
+        <v>1909</v>
+      </c>
+      <c r="M356" s="3"/>
+      <c r="N356" s="3">
+        <v>1</v>
+      </c>
+      <c r="O356" s="3">
+        <v>75</v>
+      </c>
+      <c r="P356" s="3" t="s">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="357" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A357" s="3">
+        <v>360</v>
+      </c>
+      <c r="B357" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C357" s="3" t="s">
+        <v>1911</v>
+      </c>
+      <c r="D357" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E357" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F357" s="3" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G357" s="3">
+        <v>102</v>
+      </c>
+      <c r="H357" s="3">
+        <v>103</v>
+      </c>
+      <c r="I357" s="3">
+        <v>102</v>
+      </c>
+      <c r="J357" s="3" t="s">
+        <v>1912</v>
+      </c>
+      <c r="K357" s="3" t="s">
+        <v>1913</v>
+      </c>
+      <c r="L357" s="3" t="s">
+        <v>1914</v>
+      </c>
+      <c r="M357" s="3"/>
+      <c r="N357" s="3">
+        <v>1</v>
+      </c>
+      <c r="O357" s="3">
+        <v>260</v>
+      </c>
+      <c r="P357" s="3" t="s">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="358" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A358" s="3">
+        <v>361</v>
+      </c>
+      <c r="B358" s="3" t="s">
+        <v>1989</v>
+      </c>
+      <c r="C358" s="3" t="s">
+        <v>1916</v>
+      </c>
+      <c r="D358" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E358" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F358" s="3" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G358" s="3">
+        <v>119</v>
+      </c>
+      <c r="H358" s="3">
+        <v>120</v>
+      </c>
+      <c r="I358" s="3">
+        <v>119</v>
+      </c>
+      <c r="J358" s="3" t="s">
+        <v>1917</v>
+      </c>
+      <c r="K358" s="3" t="s">
+        <v>1918</v>
+      </c>
+      <c r="L358" s="3" t="s">
+        <v>1919</v>
+      </c>
+      <c r="M358" s="3"/>
+      <c r="N358" s="3">
+        <v>1</v>
+      </c>
+      <c r="O358" s="3">
+        <v>210</v>
+      </c>
+      <c r="P358" s="3" t="s">
+        <v>1917</v>
+      </c>
+    </row>
+    <row r="359" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A359" s="3">
+        <v>362</v>
+      </c>
+      <c r="B359" s="3" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C359" s="3" t="s">
+        <v>1920</v>
+      </c>
+      <c r="D359" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E359" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F359" s="3" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G359" s="3">
+        <v>149</v>
+      </c>
+      <c r="H359" s="3">
+        <v>150</v>
+      </c>
+      <c r="I359" s="3">
+        <v>149</v>
+      </c>
+      <c r="J359" s="3" t="s">
+        <v>1921</v>
+      </c>
+      <c r="K359" s="3" t="s">
+        <v>1922</v>
+      </c>
+      <c r="L359" s="3" t="s">
+        <v>1923</v>
+      </c>
+      <c r="M359" s="3"/>
+      <c r="N359" s="3">
+        <v>1</v>
+      </c>
+      <c r="O359" s="3">
+        <v>150</v>
+      </c>
+      <c r="P359" s="3" t="s">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="360" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A360" s="3">
+        <v>363</v>
+      </c>
+      <c r="B360" s="3" t="s">
+        <v>1990</v>
+      </c>
+      <c r="C360" s="3" t="s">
+        <v>1925</v>
+      </c>
+      <c r="D360" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E360" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F360" s="3" t="s">
+        <v>1926</v>
+      </c>
+      <c r="G360" s="3">
+        <v>44</v>
+      </c>
+      <c r="H360" s="3">
+        <v>45</v>
+      </c>
+      <c r="I360" s="3">
+        <v>44</v>
+      </c>
+      <c r="J360" s="3" t="s">
+        <v>1927</v>
+      </c>
+      <c r="K360" s="3" t="s">
+        <v>1928</v>
+      </c>
+      <c r="L360" s="3" t="s">
+        <v>1929</v>
+      </c>
+      <c r="M360" s="3"/>
+      <c r="N360" s="3">
+        <v>1</v>
+      </c>
+      <c r="O360" s="3">
+        <v>45</v>
+      </c>
+      <c r="P360" s="3" t="s">
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="361" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A361" s="3">
+        <v>364</v>
+      </c>
+      <c r="B361" s="3" t="s">
+        <v>1991</v>
+      </c>
+      <c r="C361" s="3" t="s">
+        <v>1931</v>
+      </c>
+      <c r="D361" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E361" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F361" s="3" t="s">
+        <v>1926</v>
+      </c>
+      <c r="G361" s="3">
+        <v>92</v>
+      </c>
+      <c r="H361" s="3">
+        <v>93</v>
+      </c>
+      <c r="I361" s="3">
+        <v>92</v>
+      </c>
+      <c r="J361" s="3" t="s">
+        <v>1932</v>
+      </c>
+      <c r="K361" s="3" t="s">
+        <v>1933</v>
+      </c>
+      <c r="L361" s="3" t="s">
+        <v>1934</v>
+      </c>
+      <c r="M361" s="3"/>
+      <c r="N361" s="3">
+        <v>1</v>
+      </c>
+      <c r="O361" s="3">
+        <v>208</v>
+      </c>
+      <c r="P361" s="3" t="s">
+        <v>1932</v>
+      </c>
+    </row>
+    <row r="362" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A362" s="3">
+        <v>365</v>
+      </c>
+      <c r="B362" s="3" t="s">
+        <v>1992</v>
+      </c>
+      <c r="C362" s="3" t="s">
+        <v>1935</v>
+      </c>
+      <c r="D362" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E362" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F362" s="3" t="s">
+        <v>1926</v>
+      </c>
+      <c r="G362" s="3">
+        <v>101</v>
+      </c>
+      <c r="H362" s="3">
+        <v>102</v>
+      </c>
+      <c r="I362" s="3">
+        <v>101</v>
+      </c>
+      <c r="J362" s="3" t="s">
+        <v>1936</v>
+      </c>
+      <c r="K362" s="3" t="s">
+        <v>1937</v>
+      </c>
+      <c r="L362" s="3" t="s">
+        <v>1938</v>
+      </c>
+      <c r="M362" s="3"/>
+      <c r="N362" s="3">
+        <v>1</v>
+      </c>
+      <c r="O362" s="3">
+        <v>102</v>
+      </c>
+      <c r="P362" s="3" t="s">
+        <v>1939</v>
+      </c>
+    </row>
+    <row r="363" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A363" s="3">
+        <v>366</v>
+      </c>
+      <c r="B363" s="3" t="s">
+        <v>1993</v>
+      </c>
+      <c r="C363" s="3" t="s">
+        <v>1940</v>
+      </c>
+      <c r="D363" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E363" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F363" s="3" t="s">
+        <v>1926</v>
+      </c>
+      <c r="G363" s="3">
+        <v>115</v>
+      </c>
+      <c r="H363" s="3">
+        <v>116</v>
+      </c>
+      <c r="I363" s="3">
+        <v>115</v>
+      </c>
+      <c r="J363" s="3" t="s">
+        <v>1941</v>
+      </c>
+      <c r="K363" s="3" t="s">
+        <v>1942</v>
+      </c>
+      <c r="L363" s="3" t="s">
+        <v>1943</v>
+      </c>
+      <c r="M363" s="3"/>
+      <c r="N363" s="3">
+        <v>1</v>
+      </c>
+      <c r="O363" s="3">
+        <v>116</v>
+      </c>
+      <c r="P363" s="3" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="364" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A364" s="3">
+        <v>367</v>
+      </c>
+      <c r="B364" s="3" t="s">
+        <v>1994</v>
+      </c>
+      <c r="C364" s="3" t="s">
+        <v>1945</v>
+      </c>
+      <c r="D364" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E364" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F364" s="3" t="s">
+        <v>1946</v>
+      </c>
+      <c r="G364" s="3">
+        <v>14</v>
+      </c>
+      <c r="H364" s="3">
+        <v>15</v>
+      </c>
+      <c r="I364" s="3">
+        <v>14</v>
+      </c>
+      <c r="J364" s="3" t="s">
+        <v>1947</v>
+      </c>
+      <c r="K364" s="3" t="s">
+        <v>1948</v>
+      </c>
+      <c r="L364" s="3" t="s">
+        <v>1949</v>
+      </c>
+      <c r="M364" s="3"/>
+      <c r="N364" s="3">
+        <v>1</v>
+      </c>
+      <c r="O364" s="3">
+        <v>173</v>
+      </c>
+      <c r="P364" s="3" t="s">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="365" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A365" s="3">
+        <v>368</v>
+      </c>
+      <c r="B365" s="3" t="s">
+        <v>1995</v>
+      </c>
+      <c r="C365" s="3" t="s">
+        <v>1950</v>
+      </c>
+      <c r="D365" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E365" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F365" s="3" t="s">
+        <v>1946</v>
+      </c>
+      <c r="G365" s="3">
+        <v>140</v>
+      </c>
+      <c r="H365" s="3">
+        <v>141</v>
+      </c>
+      <c r="I365" s="3">
+        <v>140</v>
+      </c>
+      <c r="J365" s="3" t="s">
+        <v>1951</v>
+      </c>
+      <c r="K365" s="3" t="s">
+        <v>1952</v>
+      </c>
+      <c r="L365" s="3" t="s">
+        <v>1953</v>
+      </c>
+      <c r="M365" s="3"/>
+      <c r="N365" s="3">
+        <v>1</v>
+      </c>
+      <c r="O365" s="3">
+        <v>141</v>
+      </c>
+      <c r="P365" s="3" t="s">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="366" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A366" s="3">
+        <v>369</v>
+      </c>
+      <c r="B366" s="3" t="s">
+        <v>1985</v>
+      </c>
+      <c r="C366" s="3" t="s">
+        <v>1954</v>
+      </c>
+      <c r="D366" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E366" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F366" s="3" t="s">
+        <v>1955</v>
+      </c>
+      <c r="G366" s="3">
+        <v>85</v>
+      </c>
+      <c r="H366" s="3">
+        <v>86</v>
+      </c>
+      <c r="I366" s="3">
+        <v>85</v>
+      </c>
+      <c r="J366" s="3" t="s">
+        <v>1956</v>
+      </c>
+      <c r="K366" s="3" t="s">
+        <v>1957</v>
+      </c>
+      <c r="L366" s="3" t="s">
+        <v>1958</v>
+      </c>
+      <c r="M366" s="3"/>
+      <c r="N366" s="3">
+        <v>1</v>
+      </c>
+      <c r="O366" s="3">
+        <v>86</v>
+      </c>
+      <c r="P366" s="3" t="s">
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="367" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A367" s="3">
+        <v>370</v>
+      </c>
+      <c r="B367" s="3" t="s">
+        <v>1996</v>
+      </c>
+      <c r="C367" s="3" t="s">
+        <v>1960</v>
+      </c>
+      <c r="D367" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="E367" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F367" s="3" t="s">
+        <v>1955</v>
+      </c>
+      <c r="G367" s="3">
+        <v>99</v>
+      </c>
+      <c r="H367" s="3">
+        <v>100</v>
+      </c>
+      <c r="I367" s="3">
+        <v>99</v>
+      </c>
+      <c r="J367" s="3" t="s">
+        <v>1961</v>
+      </c>
+      <c r="K367" s="3" t="s">
+        <v>1962</v>
+      </c>
+      <c r="L367" s="3" t="s">
+        <v>1963</v>
+      </c>
+      <c r="M367" s="3"/>
+      <c r="N367" s="3">
+        <v>1</v>
+      </c>
+      <c r="O367" s="3">
+        <v>185</v>
+      </c>
+      <c r="P367" s="3" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="368" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A368" s="3">
+        <v>371</v>
+      </c>
+      <c r="B368" s="3" t="s">
+        <v>1997</v>
+      </c>
+      <c r="C368" s="3" t="s">
+        <v>1964</v>
+      </c>
+      <c r="D368" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E368" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F368" s="3" t="s">
+        <v>1965</v>
+      </c>
+      <c r="G368" s="3">
+        <v>51</v>
+      </c>
+      <c r="H368" s="3">
+        <v>52</v>
+      </c>
+      <c r="I368" s="3">
+        <v>51</v>
+      </c>
+      <c r="J368" s="3" t="s">
+        <v>1966</v>
+      </c>
+      <c r="K368" s="3" t="s">
+        <v>1967</v>
+      </c>
+      <c r="L368" s="3" t="s">
+        <v>1968</v>
+      </c>
+      <c r="M368" s="3"/>
+      <c r="N368" s="3">
+        <v>1</v>
+      </c>
+      <c r="O368" s="3">
+        <v>106</v>
+      </c>
+      <c r="P368" s="3" t="s">
+        <v>1966</v>
+      </c>
+    </row>
+    <row r="369" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A369" s="3">
+        <v>372</v>
+      </c>
+      <c r="B369" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="C369" s="3" t="s">
+        <v>1969</v>
+      </c>
+      <c r="D369" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E369" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F369" s="3" t="s">
+        <v>1970</v>
+      </c>
+      <c r="G369" s="3">
+        <v>119</v>
+      </c>
+      <c r="H369" s="3">
+        <v>122</v>
+      </c>
+      <c r="I369" s="3">
+        <v>119</v>
+      </c>
+      <c r="J369" s="3" t="s">
+        <v>1971</v>
+      </c>
+      <c r="K369" s="3" t="s">
+        <v>1972</v>
+      </c>
+      <c r="L369" s="3" t="s">
+        <v>1973</v>
+      </c>
+      <c r="M369" s="3"/>
+      <c r="N369" s="3">
+        <v>1</v>
+      </c>
+      <c r="O369" s="3">
+        <v>231</v>
+      </c>
+      <c r="P369" s="3" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="370" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A370" s="3">
+        <v>373</v>
+      </c>
+      <c r="B370" s="3" t="s">
+        <v>1510</v>
+      </c>
+      <c r="C370" s="3" t="s">
+        <v>1975</v>
+      </c>
+      <c r="D370" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E370" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F370" s="3" t="s">
+        <v>1976</v>
+      </c>
+      <c r="G370" s="3">
+        <v>112</v>
+      </c>
+      <c r="H370" s="3">
+        <v>113</v>
+      </c>
+      <c r="I370" s="3">
+        <v>112</v>
+      </c>
+      <c r="J370" s="3" t="s">
+        <v>1977</v>
+      </c>
+      <c r="K370" s="3" t="s">
+        <v>1978</v>
+      </c>
+      <c r="L370" s="3" t="s">
+        <v>1979</v>
+      </c>
+      <c r="M370" s="3"/>
+      <c r="N370" s="3">
+        <v>1</v>
+      </c>
+      <c r="O370" s="3">
+        <v>113</v>
+      </c>
+      <c r="P370" s="3" t="s">
+        <v>1980</v>
       </c>
     </row>
   </sheetData>
